--- a/docs/xlsx/jobs-2026-10-26.xlsx
+++ b/docs/xlsx/jobs-2026-10-26.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="610">
   <si>
     <t>Title</t>
   </si>
@@ -40,6 +40,465 @@
     <t>Link</t>
   </si>
   <si>
+    <t>Adventure Leader</t>
+  </si>
+  <si>
+    <t>City of Albuquerque | Parks and Recreation</t>
+  </si>
+  <si>
+    <t>Albuquerque, NM</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>$12 per hour</t>
+  </si>
+  <si>
+    <t>outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-adventure-leader-albuquerque-new-mexico/4096879391</t>
+  </si>
+  <si>
+    <t>Assistant Crew Lead</t>
+  </si>
+  <si>
+    <t>Rocky Mountain Youth Corps</t>
+  </si>
+  <si>
+    <t>Taos, NM</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$18.50 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-crew-lead-taos-new-mexico/8257545896</t>
+  </si>
+  <si>
+    <t>Assistant Director/Naturalist</t>
+  </si>
+  <si>
+    <t>Stillman Nature Center</t>
+  </si>
+  <si>
+    <t>South Barrington, IL</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$25 - $30 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-directornaturalist-south-barrington-illinois/4673491891</t>
+  </si>
+  <si>
+    <t>Assistant Wildlife Biologist</t>
+  </si>
+  <si>
+    <t>Pulama Lanai</t>
+  </si>
+  <si>
+    <t>Lanai City, HI</t>
+  </si>
+  <si>
+    <t>$60,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-wildlife-biologist-lanai-city-hawaii/2334945891</t>
+  </si>
+  <si>
+    <t>Clean Water Associate</t>
+  </si>
+  <si>
+    <t>Environment America</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>The target annual compensation for this entry-level position is $40,000 in the first year.</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-clean-water-associate-portland-oregon/6989597973</t>
+  </si>
+  <si>
+    <t>Conservation Crew Member</t>
+  </si>
+  <si>
+    <t>$17.50 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-crew-member-taos-new-mexico/9513873417</t>
+  </si>
+  <si>
+    <t>Conservation Crew Supervisor</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$19.50 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-crew-supervisor-taos-new-mexico/1893022006</t>
+  </si>
+  <si>
+    <t>Conservation Easement Monitoring Specialist</t>
+  </si>
+  <si>
+    <t>Minnesota Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Duluth, Minnesota, MN</t>
+  </si>
+  <si>
+    <t>$56,146 - $81,891 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-easement-monitoring-specialist-duluth-minnesota-minnesota/5410533722</t>
+  </si>
+  <si>
+    <t>Contract &amp; Financial Administration Specialist</t>
+  </si>
+  <si>
+    <t>Upper Colorado Environmental Plant Center</t>
+  </si>
+  <si>
+    <t>Meeker, CO</t>
+  </si>
+  <si>
+    <t>$62,000 - $68,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-contract--financial-administration-specialist-meeker-colorado/2060710697</t>
+  </si>
+  <si>
+    <t>District Forester (Lassen Forestry District)</t>
+  </si>
+  <si>
+    <t>Sierra Pacific Industries</t>
+  </si>
+  <si>
+    <t>Anderson, CA</t>
+  </si>
+  <si>
+    <t>$70,000 - $110,000 per year</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-district-forester-lassen-forestry-district-anderson-california/8500404001</t>
+  </si>
+  <si>
+    <t>District Tech</t>
+  </si>
+  <si>
+    <t>James River SCD</t>
+  </si>
+  <si>
+    <t>Ellendale, ND</t>
+  </si>
+  <si>
+    <t>$20 - $22 per hour</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-district-tech-ellendale-north-dakota/8315777856</t>
+  </si>
+  <si>
+    <t>Environmental Education Internship</t>
+  </si>
+  <si>
+    <t>Florida Keys Wild Bird Rehabilitation Center</t>
+  </si>
+  <si>
+    <t>Tavernier, FL</t>
+  </si>
+  <si>
+    <t>$500 per month</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-education-internship-tavernier-florida/2037696557</t>
+  </si>
+  <si>
+    <t>Environmental Field Organizer</t>
+  </si>
+  <si>
+    <t>Green Corps</t>
+  </si>
+  <si>
+    <t>Oakland, CA</t>
+  </si>
+  <si>
+    <t>For positions starting in August 2027, the target annual compensation is $41,000 (but compensation may range between $41,000 and $44,450 depending on location).</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-field-organizer-oakland-california/1195956283</t>
+  </si>
+  <si>
+    <t>Atlanta, GA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-field-organizer-atlanta-georgia/8191823111</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-field-organizer-boston-massachusetts/9677189879</t>
+  </si>
+  <si>
+    <t>Minneapolis, MN</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-field-organizer-minneapolis-minnesota/2917173938</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-field-organizer-seattle-washington/6327839985</t>
+  </si>
+  <si>
+    <t>Faculty Member in Chemistry</t>
+  </si>
+  <si>
+    <t>College of the Atlantic</t>
+  </si>
+  <si>
+    <t>Bar Harbor, ME</t>
+  </si>
+  <si>
+    <t>Faculty / Postdoc</t>
+  </si>
+  <si>
+    <t>$75,000 - $105,000 per year</t>
+  </si>
+  <si>
+    <t>ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-faculty-member-in-chemistry-bar-harbor-maine/8332952026</t>
+  </si>
+  <si>
+    <t>Forests Projects Coordinator</t>
+  </si>
+  <si>
+    <t>Alliance for the Chesapeake Bay</t>
+  </si>
+  <si>
+    <t>Lancaster, PA</t>
+  </si>
+  <si>
+    <t>$50,000 - $56,000 per year</t>
+  </si>
+  <si>
+    <t>forestry-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forests-projects-coordinator-lancaster-pennsylvania/1788381532</t>
+  </si>
+  <si>
+    <t>Full-Time Seasonal State Parks Resource Crew</t>
+  </si>
+  <si>
+    <t>Georgia Department of Natural Resource - State Parks Division</t>
+  </si>
+  <si>
+    <t>Social Circle, GA</t>
+  </si>
+  <si>
+    <t>$14 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-full-time-seasonal-state-parks-resource-crew-social-circle-georgia/6394270191</t>
+  </si>
+  <si>
+    <t>Invasive Species Technician 1</t>
+  </si>
+  <si>
+    <t>Tualatin Soil and Water Conservation District</t>
+  </si>
+  <si>
+    <t>Hillsboro, OR</t>
+  </si>
+  <si>
+    <t>$57,593 - $66,232 per year</t>
+  </si>
+  <si>
+    <t>botany-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-invasive-species-technician-1-hillsboro-oregon/9829601852</t>
+  </si>
+  <si>
+    <t>Magdalena Ranger District Archeologist Project Organizer</t>
+  </si>
+  <si>
+    <t>Magdelena, NM</t>
+  </si>
+  <si>
+    <t>$29.90 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-magdalena-ranger-district-archeologist-project-organizer-magdelena-new-mexico/3099624490</t>
+  </si>
+  <si>
+    <t>Naturalist</t>
+  </si>
+  <si>
+    <t>Premier Alaska Tours Inc.</t>
+  </si>
+  <si>
+    <t>Healy, AK</t>
+  </si>
+  <si>
+    <t>$1,200 - $1,300 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-naturalist-healy-alaska/4934548845</t>
+  </si>
+  <si>
+    <t>PCSU Forestry Rangeland Planner</t>
+  </si>
+  <si>
+    <t>Hawaii Division of Forestry and Wildlife</t>
+  </si>
+  <si>
+    <t>Kahului, HI</t>
+  </si>
+  <si>
+    <t>$4,376 - $5,082.56 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-pcsu-forestry-rangeland-planner-kahului-hawaii/7526175658</t>
+  </si>
+  <si>
+    <t>Reforestation Program Senior Specialist</t>
+  </si>
+  <si>
+    <t>National Forest Foundation</t>
+  </si>
+  <si>
+    <t>Gravesboro, CA</t>
+  </si>
+  <si>
+    <t>$105,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-reforestation-program-senior-specialist-gravesboro-california/2614602669</t>
+  </si>
+  <si>
+    <t>Sandia Ranger District Archeologist Project Lead</t>
+  </si>
+  <si>
+    <t>Tijeras, NM</t>
+  </si>
+  <si>
+    <t>$24.44 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sandia-ranger-district-archeologist-project-lead-tijeras-new-mexico/3333535215</t>
+  </si>
+  <si>
+    <t>Shared Range Archeologist Project Lead</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-shared-range-archeologist-project-lead-albuquerque-new-mexico/3688486792</t>
+  </si>
+  <si>
+    <t>Special Events Staff</t>
+  </si>
+  <si>
+    <t>San Diego Natural History Museum</t>
+  </si>
+  <si>
+    <t>San Diego, CA</t>
+  </si>
+  <si>
+    <t>$20 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-special-events-staff-san-diego-california/3488018445</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>New Mexico Wilderness Alliance</t>
+  </si>
+  <si>
+    <t>$80,000 - $85,000 per year</t>
+  </si>
+  <si>
+    <t>policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-staff-attorney-albuquerque-new-mexico/8231531974</t>
+  </si>
+  <si>
+    <t>Stream Habitat Supervisor</t>
+  </si>
+  <si>
+    <t>Brainerd, Minnesota, MN</t>
+  </si>
+  <si>
+    <t>$81,007 - $116,782 per year</t>
+  </si>
+  <si>
+    <t>fisheries-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-stream-habitat-supervisor-brainerd-minnesota-minnesota/5123158677</t>
+  </si>
+  <si>
+    <t>Summer Environmental Education Intern</t>
+  </si>
+  <si>
+    <t>Dauphin Island Sea Lab</t>
+  </si>
+  <si>
+    <t>Dauphin Island, AL</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>A $4,000 stipend, paid either bi-weekly or monthly.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-summer-environmental-education-intern-dauphin-island-alabama/8116391488</t>
+  </si>
+  <si>
     <t>TerraCorp Community Engagement Coordinator at Farming Falmouth</t>
   </si>
   <si>
@@ -49,9 +508,6 @@
     <t>Falmouth, MA</t>
   </si>
   <si>
-    <t>AmeriCorps</t>
-  </si>
-  <si>
     <t>$19,656 per year</t>
   </si>
   <si>
@@ -61,6 +517,15 @@
     <t>https://www.conservationjobboard.com/job-listing-terracorp-community-engagement-coordinator-at-farming-falmouth-falmouth-massachusetts/6302585700</t>
   </si>
   <si>
+    <t>Virginia Conservation Campaigner</t>
+  </si>
+  <si>
+    <t>Richmond, VA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-virginia-conservation-campaigner-richmond-virginia/9352649067</t>
+  </si>
+  <si>
     <t>Wildlife Biologist</t>
   </si>
   <si>
@@ -70,9 +535,6 @@
     <t>Kingston, WA</t>
   </si>
   <si>
-    <t>Permanent</t>
-  </si>
-  <si>
     <t>$78,500 - $91,500 per year</t>
   </si>
   <si>
@@ -82,6 +544,21 @@
     <t>https://www.conservationjobboard.com/job-listing-wildlife-biologist-kingston-washington/8083172533</t>
   </si>
   <si>
+    <t>Wildlife Specialist (Carnivore)</t>
+  </si>
+  <si>
+    <t>White Oak Conservation</t>
+  </si>
+  <si>
+    <t>Yulee, FL</t>
+  </si>
+  <si>
+    <t>Negotiable</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-specialist-carnivore-yulee-florida/2206975033</t>
+  </si>
+  <si>
     <t>Youth &amp; Community Programs Manager</t>
   </si>
   <si>
@@ -98,6 +575,1275 @@
   </si>
   <si>
     <t>https://www.conservationjobboard.com/job-listing-youth--community-programs-manager-lakewood-colorado/4153225414</t>
+  </si>
+  <si>
+    <t>Senior Construction Project Manager</t>
+  </si>
+  <si>
+    <t>Green Hammer</t>
+  </si>
+  <si>
+    <t>Portland, Oregon, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t>100,000 and above</t>
+  </si>
+  <si>
+    <t>Green Building</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/senior-construction-project-manager/</t>
+  </si>
+  <si>
+    <t>Vice President of Horticulture</t>
+  </si>
+  <si>
+    <t>Missouri Botanical Garden</t>
+  </si>
+  <si>
+    <t>St. Louis, Missouri, United States</t>
+  </si>
+  <si>
+    <t>Horticulture / Gardening / Landscaping</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/vice-president-of-horticulture/</t>
+  </si>
+  <si>
+    <t>2027 Uwharrie Prescribed Fire/Fuels Module Lead</t>
+  </si>
+  <si>
+    <t>The Ember Alliance</t>
+  </si>
+  <si>
+    <t>Troy, North Carolina</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/95f8c4114cf640bc9343849877b54fbf-2027-uwharrie-prescribed-firefuels-module-lead-the-ember-alliance-troy</t>
+  </si>
+  <si>
+    <t>4-H Foundation Administrative and Events Coordinator</t>
+  </si>
+  <si>
+    <t>University of Florida 4-H Foundation</t>
+  </si>
+  <si>
+    <t>Jacksonville, Florida</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 25.00/hour</t>
+  </si>
+  <si>
+    <t>Agriculture, Children Youth, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/423e3e9652214ebda03de08adc8ceb21-4-h-foundation-administrative-and-events-coordinator-university-of-florida-4-h-foundation-jacksonville</t>
+  </si>
+  <si>
+    <t>Administrative Assistant (Onsite)</t>
+  </si>
+  <si>
+    <t>Our Place of New Trier</t>
+  </si>
+  <si>
+    <t>Wilmette, Illinois</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a5031cc3ea49413dac42af589052ac93-administrative-assistant-onsite-our-place-of-new-trier-wilmette</t>
+  </si>
+  <si>
+    <t>Agroflorestor(a)</t>
+  </si>
+  <si>
+    <t>Eco Caminhos</t>
+  </si>
+  <si>
+    <t>Nova Friburgo, Rio de Janeiro, BR</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Agriculture, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f2c60ab12aac4e0da82abaf5075b91fd-agroflorestora-eco-caminhos-nova-friburgo</t>
+  </si>
+  <si>
+    <t>Anti-Trafficking Services Caseworker</t>
+  </si>
+  <si>
+    <t>Preble Street</t>
+  </si>
+  <si>
+    <t>Portland, Maine</t>
+  </si>
+  <si>
+    <t>USD 23.82 - 23.82/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7b08f41f67c748a282a96e86886ee5b7-anti-trafficking-services-caseworker-preble-street-portland</t>
+  </si>
+  <si>
+    <t>Anti-Trafficking Services Outreach Specialist</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c036d458857942589f0d2b91fd738284-anti-trafficking-services-outreach-specialist-preble-street-portland</t>
+  </si>
+  <si>
+    <t>Assistant, Associate or Full Professor in Community Psychology</t>
+  </si>
+  <si>
+    <t>The American University in Cairo</t>
+  </si>
+  <si>
+    <t>Hewlett, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/bd6ab565a98a466c865be0f5c1ce0ca5-assistant-associate-or-full-professor-in-community-psychology-the-american-university-in-cairo-hewlett</t>
+  </si>
+  <si>
+    <t>Associate Supervising/Supervising Attorney</t>
+  </si>
+  <si>
+    <t>UnLocal, Inc.</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/00ac658fa0a6473693405df2365938c5-associate-supervisingsupervising-attorney-unlocal-inc-new-york</t>
+  </si>
+  <si>
+    <t>Business Development Associate</t>
+  </si>
+  <si>
+    <t>The Horticultural Society of New York</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/47fc5074f7124c1e91611976afa00246-business-development-associate-the-horticultural-society-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Business Support Assistant to the Deputy Regional Director</t>
+  </si>
+  <si>
+    <t>World Food Programme</t>
+  </si>
+  <si>
+    <t>Panama City, Panamá Province, PA</t>
+  </si>
+  <si>
+    <t>Community Development, Climate Change, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/77ac6e62c4094b979064f9ce95edb556-business-support-assistant-to-the-deputy-regional-director-world-food-programme-panama-city</t>
+  </si>
+  <si>
+    <t>Case Supervisor and Volunteer Recruiter</t>
+  </si>
+  <si>
+    <t>GUARDIAN PARTNERS</t>
+  </si>
+  <si>
+    <t>Salem, Oregon</t>
+  </si>
+  <si>
+    <t>Disability, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/68727a599860431c972cc84279265394-case-supervisor-and-volunteer-recruiter-guardian-partners-salem</t>
+  </si>
+  <si>
+    <t>Chief Advancement Officer</t>
+  </si>
+  <si>
+    <t>Lowcountry Land Trust</t>
+  </si>
+  <si>
+    <t>Charleston, South Carolina</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 118000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ab3a44b24a224e22a1697a40d65619bf-chief-advancement-officer-lowcountry-land-trust-charleston</t>
+  </si>
+  <si>
+    <t>Chief Financial Officer, ABCD</t>
+  </si>
+  <si>
+    <t>Eos Transition Partners</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 210000.00 - 240000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/1ee4746094134b8bb1f2747fdc9858fd-chief-financial-officer-abcd-eos-transition-partners-boston</t>
+  </si>
+  <si>
+    <t>Chief of Schools</t>
+  </si>
+  <si>
+    <t>Colorado Schools Fund</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 215000.00 - 215000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5bb309c0b889433b9f2676a6751190b3-chief-of-schools-colorado-schools-fund-denver</t>
+  </si>
+  <si>
+    <t>Communications Director</t>
+  </si>
+  <si>
+    <t>The Explorers Club</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6b08b9e1ba94458a87284eb3ec573b8d-communications-director-the-explorers-club-new-york</t>
+  </si>
+  <si>
+    <t>Communities Program Associate</t>
+  </si>
+  <si>
+    <t>Great Plains Institute</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/68cc6988c43741baa1d396ef54790bd2-communities-program-associate-great-plains-institute-minneapolis</t>
+  </si>
+  <si>
+    <t>Community Liaison</t>
+  </si>
+  <si>
+    <t>Ecology Center, Ann Arbor</t>
+  </si>
+  <si>
+    <t>Remote (Michigan)</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5e0206d5d2b74d1b85d402df9afaec8b-community-liaison-ecology-center-ann-arbor-ann-arbor</t>
+  </si>
+  <si>
+    <t>Controller (Director Level)</t>
+  </si>
+  <si>
+    <t>Point Foundation</t>
+  </si>
+  <si>
+    <t>Remote (Los Angeles, California)</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1b5e1248544d4b3aae833dc1253a86b1-controller-director-level-point-foundation-los-angeles</t>
+  </si>
+  <si>
+    <t>Cook II</t>
+  </si>
+  <si>
+    <t>Central Union Mission</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 39000.00 - 42000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6fac334154fb46efb08bde6b69c442ea-cook-ii-central-union-mission-washington</t>
+  </si>
+  <si>
+    <t>Data and Policy Analyst</t>
+  </si>
+  <si>
+    <t>California Pan-Ethnic Health Network - CPEHN</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c3c8aa234ed54d5ca4bd1fb852c7d495-data-and-policy-analyst-california-pan-ethnic-health-network-cpehn-oakland</t>
+  </si>
+  <si>
+    <t>Database Specialist</t>
+  </si>
+  <si>
+    <t>Piedmont Environmental Council</t>
+  </si>
+  <si>
+    <t>Warrenton, VA</t>
+  </si>
+  <si>
+    <t>USD 31.25 - 43.26/hour</t>
+  </si>
+  <si>
+    <t>Agriculture, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/870bd777c3e74ca697aa8ce6db2b02f8-database-specialist-piedmont-environmental-council-warrenton</t>
+  </si>
+  <si>
+    <t>Big Brothers Big Sisters of New York City</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7d9715eaa0784276ad89eb99545a4d95-database-specialist-big-brothers-big-sisters-of-new-york-city-new-york</t>
+  </si>
+  <si>
+    <t>Development and Strategic Partnerships Manager - NC Rural Center</t>
+  </si>
+  <si>
+    <t>Armstrong McGuire &amp; Associates</t>
+  </si>
+  <si>
+    <t>Raleigh, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/2960fb5b108d46019ff1e42c82586456-development-and-strategic-partnerships-manager-nc-rural-center-armstrong-mcguire-associates-raleigh</t>
+  </si>
+  <si>
+    <t>Development Coordinator, East Region</t>
+  </si>
+  <si>
+    <t>Facing History and Ourselves</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8c738cc9c8894cfa82d7beb5995ec753-development-coordinator-east-region-facing-history-and-ourselves-new-york</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>Dairy Arts Center</t>
+  </si>
+  <si>
+    <t>Boulder, Colorado</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c200cc0101aa444e96c86402f2b9553c-development-director-dairy-arts-center-boulder</t>
+  </si>
+  <si>
+    <t>Catholic Charities of Oregon</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c10efbeaea9b4815ac98dc78f89a72dc-development-director-catholic-charities-of-oregon-portland</t>
+  </si>
+  <si>
+    <t>Development Director, Boston</t>
+  </si>
+  <si>
+    <t>UNCF</t>
+  </si>
+  <si>
+    <t>USD 79000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dc2100117493419c948e438688283d33-development-director-boston-uncf-boston</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>West Side Montessori School</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/69d21822511b48129337b09dafcd3994-director-of-development-west-side-montessori-school-new-york</t>
+  </si>
+  <si>
+    <t>Director of Fund Development</t>
+  </si>
+  <si>
+    <t>The Salvation Army National Headquarters</t>
+  </si>
+  <si>
+    <t>Alexandria, Virginia</t>
+  </si>
+  <si>
+    <t>USD 80930.00 - 105104.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/39de093d9a4b4a9abd45a5bb304e4174-director-of-fund-development-the-salvation-army-national-headquarters-alexandria</t>
+  </si>
+  <si>
+    <t>Director of Membership and Marketing</t>
+  </si>
+  <si>
+    <t>National Communication Association</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ae2af184dcff4ce0a8b45a08f2fd6ad4-director-of-membership-and-marketing-national-communication-association-washington</t>
+  </si>
+  <si>
+    <t>Director of Organizing</t>
+  </si>
+  <si>
+    <t>Direct Action &amp; Research Training Center</t>
+  </si>
+  <si>
+    <t>Roanoke, Virginia</t>
+  </si>
+  <si>
+    <t>USD 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/537508bf539c4e9092ee7bd85d029ee3-director-of-organizing-direct-action-research-training-center-roanoke</t>
+  </si>
+  <si>
+    <t>Director of Public Policy</t>
+  </si>
+  <si>
+    <t>Massachusetts Housing &amp; Shelter Alliance</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2164b2c4c7fc4965bc962d4821270701-director-of-public-policy-massachusetts-housing-shelter-alliance-boston</t>
+  </si>
+  <si>
+    <t>Director of Retreats</t>
+  </si>
+  <si>
+    <t>Loretto Community (Loretto Motherhouse)</t>
+  </si>
+  <si>
+    <t>Loretto, Kentucky</t>
+  </si>
+  <si>
+    <t>Community Development, Environment, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eea78e2602e34e3aba04b255959d15ad-director-of-retreats-loretto-community-loretto-motherhouse-loretto</t>
+  </si>
+  <si>
+    <t>Director, Development Operations</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9e1ff562ceb24a2785784a093196fb0f-director-development-operations-point-foundation-los-angeles</t>
+  </si>
+  <si>
+    <t>Director, Gifts and Endowment</t>
+  </si>
+  <si>
+    <t>North Carolina Justice Center</t>
+  </si>
+  <si>
+    <t>USD 118000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Education, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7f188b38701748b29288b5793acc6e63-director-gifts-and-endowment-north-carolina-justice-center-raleigh</t>
+  </si>
+  <si>
+    <t>Director, Program Operations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b06e21e9f8f04ff9ae159d6da3c910a2-director-program-operations-point-foundation-los-angeles</t>
+  </si>
+  <si>
+    <t>Disability Specialist and Victim Advocate</t>
+  </si>
+  <si>
+    <t>The Initiative</t>
+  </si>
+  <si>
+    <t>Lakewood, Colorado</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Sexual Abuse Human Trafficking, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/006525fe41ea49348e11fc5d4d73682c-disability-specialist-and-victim-advocate-the-initiative-lakewood</t>
+  </si>
+  <si>
+    <t>Driver</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/39e4f6dc91b84e6088004e8c9ded363f-driver-central-union-mission-washington</t>
+  </si>
+  <si>
+    <t>Education and Employment Coordinator</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0123f109b8614aa8b42023c593887adc-education-and-employment-coordinator-central-union-mission-washington</t>
+  </si>
+  <si>
+    <t>Executive Assistant</t>
+  </si>
+  <si>
+    <t>BrightFocus Foundation</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/35aba8525482472c9129b57f6dc12d72-executive-assistant-brightfocus-foundation-washington</t>
+  </si>
+  <si>
+    <t>Executive Camp Director</t>
+  </si>
+  <si>
+    <t>Canoe Island French Camp</t>
+  </si>
+  <si>
+    <t>Orcas, Washington</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/30015113e2164a4e80d2cb437a978e5c-executive-camp-director-canoe-island-french-camp-orcas</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Multi-service Eating Disorders Association</t>
+  </si>
+  <si>
+    <t>Newton, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7daf35c63e8b4923a9a9556dfc4f2143-executive-director-multi-service-eating-disorders-association-newton</t>
+  </si>
+  <si>
+    <t>Executive Office Coordinator</t>
+  </si>
+  <si>
+    <t>JCC Association</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ff15fdba5c954f0cb9115e45b6a7d94a-executive-office-coordinator-jcc-association-new-york</t>
+  </si>
+  <si>
+    <t>Facility Maintenance Manager</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6e7ab7fe8c5c44cbb4f295e659015cf1-facility-maintenance-manager-central-union-mission-washington</t>
+  </si>
+  <si>
+    <t>Family Services Manager</t>
+  </si>
+  <si>
+    <t>Christopher's Haven Boston</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96d9200673944f418868f831c3287fca-family-services-manager-christophers-haven-boston-boston</t>
+  </si>
+  <si>
+    <t>Family Stability Manager ($85-$100K)</t>
+  </si>
+  <si>
+    <t>Playtime Project</t>
+  </si>
+  <si>
+    <t>Greenbelt, Maryland</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/895beeaa7378494c8de4713638b05551-family-stability-manager-85-100k-playtime-project-greenbelt</t>
+  </si>
+  <si>
+    <t>Food Education Training Manager</t>
+  </si>
+  <si>
+    <t>FoodCorps</t>
+  </si>
+  <si>
+    <t>USD 82400.00 - 82400.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1d371435a0f948c9ab7b923b3c5d82af-food-education-training-manager-foodcorps-portland</t>
+  </si>
+  <si>
+    <t>Full-Time Psychotherapist</t>
+  </si>
+  <si>
+    <t>Community Counseling and Mediation</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 67000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Mental Health, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dc41b7ef7b2c42bbbc132117d0d65603-full-time-psychotherapist-community-counseling-and-mediation-kings-county</t>
+  </si>
+  <si>
+    <t>Grants and CASSR Administrator - Sociology</t>
+  </si>
+  <si>
+    <t>New York University</t>
+  </si>
+  <si>
+    <t>USD 77000.00 - 82000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/0744963756d942acadab76725b83d8c3-grants-and-cassr-administrator-sociology-new-york-university-new-york</t>
+  </si>
+  <si>
+    <t>Housing Intake Coordinator</t>
+  </si>
+  <si>
+    <t>Access Living of Metropolitan Chicago</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 54500.00 - 59500.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a731d6f387134a15bd94da9d74a67b55-housing-intake-coordinator-access-living-of-metropolitan-chicago-chicago</t>
+  </si>
+  <si>
+    <t>Housing Specialist</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/06a19d5f95334e63ba163ac911945e2f-housing-specialist-preble-street-portland</t>
+  </si>
+  <si>
+    <t>Immigration Attorney</t>
+  </si>
+  <si>
+    <t>CLEAN Carwash Worker Center</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Entrepreneurship, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f7f320832ebf46ba9da9246796a82f06-immigration-attorney-clean-carwash-worker-center-los-angeles</t>
+  </si>
+  <si>
+    <t>Individual and Major Giving Director</t>
+  </si>
+  <si>
+    <t>Encore Community Services</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Seniors Retirement, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/77bff999000846eabb1804c14fcd2c37-individual-and-major-giving-director-encore-community-services-new-york</t>
+  </si>
+  <si>
+    <t>Inland Empire Education and Outreach Coordinator</t>
+  </si>
+  <si>
+    <t>San Bernardino, California</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8b45e3c7e7064821a2d8bfc21c072c62-inland-empire-education-and-outreach-coordinator-clean-carwash-worker-center-san-bernardino</t>
+  </si>
+  <si>
+    <t>Institutional Giving Manager &amp; Grant Writer</t>
+  </si>
+  <si>
+    <t>Dayenu: A Jewish Call to Climate Action</t>
+  </si>
+  <si>
+    <t>USD 35000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f14ad49ed910427284f9825b2014ea67-institutional-giving-manager-grant-writer-dayenu-a-jewish-call-to-climate-action-new-york</t>
+  </si>
+  <si>
+    <t>Lead, Reviews (Math)</t>
+  </si>
+  <si>
+    <t>EdReports</t>
+  </si>
+  <si>
+    <t>USD 102824.00 - 139114.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7d5fb6f10b4747fc92a654b59ca8e64f-lead-reviews-math-edreports-raleigh</t>
+  </si>
+  <si>
+    <t>LEGAL AID STAFF ATTORNEY BENEFITS UNIT (CWJC)</t>
+  </si>
+  <si>
+    <t>Community Legal Aid &amp; Affiliate</t>
+  </si>
+  <si>
+    <t>Worcester, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 109000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a9c274d40038447fbae9d3ac93590164-legal-aid-staff-attorney-benefits-unit-cwjc-community-legal-aid-affiliate-worcester</t>
+  </si>
+  <si>
+    <t>Litigation Attorney</t>
+  </si>
+  <si>
+    <t>Disability Law Center</t>
+  </si>
+  <si>
+    <t>Remote (Massachusetts)</t>
+  </si>
+  <si>
+    <t>USD 88200.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e7ddc6824db640799b34941079839b43-litigation-attorney-disability-law-center-boston</t>
+  </si>
+  <si>
+    <t>Major Gifts Officer, East Region</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6bf08a6b3ce44171adcd40a5095063a0-major-gifts-officer-east-region-facing-history-and-ourselves-boston</t>
+  </si>
+  <si>
+    <t>Marketing and Administrative Assistant</t>
+  </si>
+  <si>
+    <t>Nu Haven Kapelye</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/acc3a372c6e14af6a9f73511dfca5b3e-marketing-and-administrative-assistant-nu-haven-kapelye-hamden</t>
+  </si>
+  <si>
+    <t>OFFICE MANAGER/FRONT DESK</t>
+  </si>
+  <si>
+    <t>IHI Therapy Center</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Lgbtq, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c789a800f5fe430a97f57053ca1ccc77-office-managerfront-desk-ihi-therapy-center-new-york</t>
+  </si>
+  <si>
+    <t>Planned Giving Director</t>
+  </si>
+  <si>
+    <t>Window to the World Communications, Inc. (WTTW/WFMT)</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9de8f5e598ed438080eeb534213f938a-planned-giving-director-window-to-the-world-communications-inc-wttwwfmt-chicago</t>
+  </si>
+  <si>
+    <t>Program Coordinator (Apprenticeship Expansion)</t>
+  </si>
+  <si>
+    <t>Building Futures (Rhode Island)</t>
+  </si>
+  <si>
+    <t>Providence, Rhode Island</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 62500.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/45c5aa8212cc453d9d64090ae12fa24a-program-coordinator-apprenticeship-expansion-building-futures-rhode-island-providence</t>
+  </si>
+  <si>
+    <t>Program Director</t>
+  </si>
+  <si>
+    <t>Association of Asian American Investment Managers</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/25e2ba7b3dbc45fbb74cb99a08adb9c7-program-director-association-of-asian-american-investment-managers-san-francisco</t>
+  </si>
+  <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>Immigrant Legal Resource Center</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 120574.50 - 129061.50/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/edcf9f08cdff4d9dbb63be1557cd8b8f-project-manager-immigrant-legal-resource-center-san-francisco</t>
+  </si>
+  <si>
+    <t>Remote (Fresno, California)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bd271f24d3134b1298d19d4dc1ce3505-project-manager-immigrant-legal-resource-center-fresno</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4dac40b0c4ec486fa2b241a9e0ba8b69-project-manager-immigrant-legal-resource-center-los-angeles</t>
+  </si>
+  <si>
+    <t>Reach Out and Read Development Specialist, WA</t>
+  </si>
+  <si>
+    <t>Positively Partners</t>
+  </si>
+  <si>
+    <t>Remote (Washington)</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/2b78b3bc7cdf4ba18b4c68c8c5a244e2-reach-out-and-read-development-specialist-wa-positively-partners-boston</t>
+  </si>
+  <si>
+    <t>Resource Protection Manager</t>
+  </si>
+  <si>
+    <t>Panthera</t>
+  </si>
+  <si>
+    <t>Mumbwa, Central Province, ZM</t>
+  </si>
+  <si>
+    <t>Animals, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca2da4ba6ea74147b4c609c5ff67a406-resource-protection-manager-panthera-mumbwa</t>
+  </si>
+  <si>
+    <t>Senior Communications Associate</t>
+  </si>
+  <si>
+    <t>American Flood Coalition</t>
+  </si>
+  <si>
+    <t>USD 77000.00 - 92000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Disaster Relief, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4853226d5b484040bf2d28e5b490ee97-senior-communications-associate-american-flood-coalition-washington</t>
+  </si>
+  <si>
+    <t>SENIOR DEVELOPMENT ASSOCIATE – Events &amp; Individual Giving POSITION DESCRIPTION</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9d2872875bca4801ac4027f74b618972-senior-development-associate-events-individual-giving-position-description-access-living-of-metropolitan-chicago-chicago</t>
+  </si>
+  <si>
+    <t>Senior HRIS Analyst - Workday</t>
+  </si>
+  <si>
+    <t>Research Foundation of CUNY</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3dc2ef53fc554190b2ca0d6f9bc772f3-senior-hris-analyst-workday-research-foundation-of-cuny-new-york</t>
+  </si>
+  <si>
+    <t>Senior Software Development Engineer, Full Stack</t>
+  </si>
+  <si>
+    <t>Gifted Savings</t>
+  </si>
+  <si>
+    <t>USD 170000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dd5dc257bb4e4a4e9903e06fd9dce025-senior-software-development-engineer-full-stack-gifted-savings-rolling-hills-estates</t>
+  </si>
+  <si>
+    <t>Senior Staff Accountant</t>
+  </si>
+  <si>
+    <t>American Association for the Study of Liver Diseases</t>
+  </si>
+  <si>
+    <t>USD 81600.00 - 102000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5f936db38a784c1397db387ada4296e5-senior-staff-accountant-american-association-for-the-study-of-liver-diseases-alexandria</t>
+  </si>
+  <si>
+    <t>Senior Staff Attorney - Rapid Response</t>
+  </si>
+  <si>
+    <t>USD 84000.00 - 84000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/78069a77f5d940f78f63c4f7480740f5-senior-staff-attorney-rapid-response-unlocal-inc-new-york</t>
+  </si>
+  <si>
+    <t>Senior Vice President</t>
+  </si>
+  <si>
+    <t>Association of Chamber of Commerce Executives</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 225000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/66d3facba9d04b3f95b06b3dd3bb2899-senior-vice-president-association-of-chamber-of-commerce-executives-alexandria</t>
+  </si>
+  <si>
+    <t>Shelter Manager</t>
+  </si>
+  <si>
+    <t>The Animal Haven, Inc.</t>
+  </si>
+  <si>
+    <t>North Haven, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 53000.00 - 53000.00/year</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/74cc7d0ebefc4b7b86042b00ac5a20ea-shelter-manager-the-animal-haven-inc-north-haven</t>
+  </si>
+  <si>
+    <t>Small Utility Project Manager I (Job #373) ($76,103 - $83,976)</t>
+  </si>
+  <si>
+    <t>Rural Community Assistance Corporation (RCAC)</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 70775.00 - 92408.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6b1233a2e2b84dbda7d5dc35aee74aab-small-utility-project-manager-i-job-373-76103-83976-rural-community-assistance-corporation-rcac-west-sacramento</t>
+  </si>
+  <si>
+    <t>Special Education Teacher ($2,500 Sign-on Bonus)</t>
+  </si>
+  <si>
+    <t>Saint Dominic's Family Services</t>
+  </si>
+  <si>
+    <t>Bronx, New York</t>
+  </si>
+  <si>
+    <t>USD 65000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c10e7c48067c46f8a5b648530dbf12db-special-education-teacher-2500-sign-on-bonus-saint-dominics-family-services-bronx</t>
+  </si>
+  <si>
+    <t>Sr. Director, Technology &amp; Systems</t>
+  </si>
+  <si>
+    <t>USD 165000.00 - 190000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fdb1c262395f487eb5a75b0bf983b1a6-sr-director-technology-systems-point-foundation-los-angeles</t>
+  </si>
+  <si>
+    <t>Sr. Manager, Strategy, Projects &amp; Special Initiatives</t>
+  </si>
+  <si>
+    <t>All Our Kin</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f4522350cd4d4d98a5473f5697722026-sr-manager-strategy-projects-special-initiatives-all-our-kin-new-haven</t>
+  </si>
+  <si>
+    <t>Staff Attorney, Detention and Deportation Defense Initiative</t>
+  </si>
+  <si>
+    <t>AFSC (American Friends Service Committee)</t>
+  </si>
+  <si>
+    <t>Newark, New Jersey</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d2737bbd99a4274895cb3d7c45b777a-staff-attorney-detention-and-deportation-defense-initiative-afsc-american-friends-service-committee-newark</t>
+  </si>
+  <si>
+    <t>Supervising Attorney</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de48dacc636e466faa5d527ea60c2ad8-supervising-attorney-unlocal-inc-new-york</t>
+  </si>
+  <si>
+    <t>Supervisor Case Management - Wellness Together</t>
+  </si>
+  <si>
+    <t>University Settlement Society of New York</t>
+  </si>
+  <si>
+    <t>USD 76476.40 - 76476.40/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/83bc43346f2f48eeb1d08a39198205f1-supervisor-case-management-wellness-together-university-settlement-society-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Tri-Lingual Comprehensive Domestic &amp; Sexual Violence Counselor/Advocate</t>
+  </si>
+  <si>
+    <t>Independence House, Inc.</t>
+  </si>
+  <si>
+    <t>Barnstable, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 37000.00 - 43500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/99a68c725a65439dbead5c54ca92b5a4-tri-lingual-comprehensive-domestic-sexual-violence-counseloradvocate-independence-house-inc-barnstable</t>
   </si>
 </sst>
 </file>
@@ -483,7 +2229,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -579,16 +2325,775 @@
         <v>24</v>
       </c>
       <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
         <v>18</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
         <v>25</v>
       </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>27</v>
+      <c r="E9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" t="s">
+        <v>95</v>
+      </c>
+      <c r="F19" t="s">
+        <v>96</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20" t="s">
+        <v>102</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" t="s">
+        <v>107</v>
+      </c>
+      <c r="F21" t="s">
+        <v>102</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B22" t="s">
+        <v>110</v>
+      </c>
+      <c r="C22" t="s">
+        <v>111</v>
+      </c>
+      <c r="D22" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" t="s">
+        <v>112</v>
+      </c>
+      <c r="F22" t="s">
+        <v>113</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" t="s">
+        <v>117</v>
+      </c>
+      <c r="F23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>119</v>
+      </c>
+      <c r="B24" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" t="s">
+        <v>121</v>
+      </c>
+      <c r="D24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>124</v>
+      </c>
+      <c r="B25" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" t="s">
+        <v>126</v>
+      </c>
+      <c r="D25" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" t="s">
+        <v>127</v>
+      </c>
+      <c r="F25" t="s">
+        <v>70</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>129</v>
+      </c>
+      <c r="B26" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" t="s">
+        <v>131</v>
+      </c>
+      <c r="D26" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" t="s">
+        <v>132</v>
+      </c>
+      <c r="F26" t="s">
+        <v>102</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="s">
+        <v>135</v>
+      </c>
+      <c r="D27" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" t="s">
+        <v>136</v>
+      </c>
+      <c r="F27" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>138</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" t="s">
+        <v>136</v>
+      </c>
+      <c r="F28" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>140</v>
+      </c>
+      <c r="B29" t="s">
+        <v>141</v>
+      </c>
+      <c r="C29" t="s">
+        <v>142</v>
+      </c>
+      <c r="D29" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" t="s">
+        <v>143</v>
+      </c>
+      <c r="F29" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>145</v>
+      </c>
+      <c r="B30" t="s">
+        <v>146</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" t="s">
+        <v>147</v>
+      </c>
+      <c r="F30" t="s">
+        <v>148</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>150</v>
+      </c>
+      <c r="B31" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" t="s">
+        <v>151</v>
+      </c>
+      <c r="D31" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" t="s">
+        <v>152</v>
+      </c>
+      <c r="F31" t="s">
+        <v>153</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>155</v>
+      </c>
+      <c r="B32" t="s">
+        <v>156</v>
+      </c>
+      <c r="C32" t="s">
+        <v>157</v>
+      </c>
+      <c r="D32" t="s">
+        <v>158</v>
+      </c>
+      <c r="E32" t="s">
+        <v>159</v>
+      </c>
+      <c r="F32" t="s">
+        <v>76</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>161</v>
+      </c>
+      <c r="B33" t="s">
+        <v>162</v>
+      </c>
+      <c r="C33" t="s">
+        <v>163</v>
+      </c>
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" t="s">
+        <v>164</v>
+      </c>
+      <c r="F33" t="s">
+        <v>165</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>167</v>
+      </c>
+      <c r="B34" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" t="s">
+        <v>168</v>
+      </c>
+      <c r="D34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" t="s">
+        <v>38</v>
+      </c>
+      <c r="F34" t="s">
+        <v>39</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>170</v>
+      </c>
+      <c r="B35" t="s">
+        <v>171</v>
+      </c>
+      <c r="C35" t="s">
+        <v>172</v>
+      </c>
+      <c r="D35" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" t="s">
+        <v>173</v>
+      </c>
+      <c r="F35" t="s">
+        <v>174</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>176</v>
+      </c>
+      <c r="B36" t="s">
+        <v>177</v>
+      </c>
+      <c r="C36" t="s">
+        <v>178</v>
+      </c>
+      <c r="D36" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" t="s">
+        <v>179</v>
+      </c>
+      <c r="F36" t="s">
+        <v>33</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>181</v>
+      </c>
+      <c r="B37" t="s">
+        <v>182</v>
+      </c>
+      <c r="C37" t="s">
+        <v>183</v>
+      </c>
+      <c r="D37" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" t="s">
+        <v>184</v>
+      </c>
+      <c r="F37" t="s">
+        <v>185</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -597,6 +3102,39 @@
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
     <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -605,7 +3143,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -644,8 +3182,58 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -653,7 +3241,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -692,8 +3280,2050 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F4" t="s">
+        <v>217</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" t="s">
+        <v>221</v>
+      </c>
+      <c r="D5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F5" t="s">
+        <v>223</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E6" t="s">
+        <v>228</v>
+      </c>
+      <c r="F6" t="s">
+        <v>229</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B7" t="s">
+        <v>226</v>
+      </c>
+      <c r="C7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D7" t="s">
+        <v>202</v>
+      </c>
+      <c r="E7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F7" t="s">
+        <v>229</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>233</v>
+      </c>
+      <c r="B8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D8" t="s">
+        <v>202</v>
+      </c>
+      <c r="E8" t="s">
+        <v>222</v>
+      </c>
+      <c r="F8" t="s">
+        <v>222</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>237</v>
+      </c>
+      <c r="B9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D9" t="s">
+        <v>202</v>
+      </c>
+      <c r="E9" t="s">
+        <v>240</v>
+      </c>
+      <c r="F9" t="s">
+        <v>241</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>243</v>
+      </c>
+      <c r="B10" t="s">
+        <v>244</v>
+      </c>
+      <c r="C10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D10" t="s">
+        <v>202</v>
+      </c>
+      <c r="E10" t="s">
+        <v>245</v>
+      </c>
+      <c r="F10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>247</v>
+      </c>
+      <c r="B11" t="s">
+        <v>248</v>
+      </c>
+      <c r="C11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E11" t="s">
+        <v>222</v>
+      </c>
+      <c r="F11" t="s">
+        <v>250</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>252</v>
+      </c>
+      <c r="B12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C12" t="s">
+        <v>254</v>
+      </c>
+      <c r="D12" t="s">
+        <v>202</v>
+      </c>
+      <c r="E12" t="s">
+        <v>245</v>
+      </c>
+      <c r="F12" t="s">
+        <v>255</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>257</v>
+      </c>
+      <c r="B13" t="s">
+        <v>258</v>
+      </c>
+      <c r="C13" t="s">
+        <v>259</v>
+      </c>
+      <c r="D13" t="s">
+        <v>202</v>
+      </c>
+      <c r="E13" t="s">
+        <v>260</v>
+      </c>
+      <c r="F13" t="s">
+        <v>261</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>263</v>
+      </c>
+      <c r="B14" t="s">
+        <v>264</v>
+      </c>
+      <c r="C14" t="s">
+        <v>265</v>
+      </c>
+      <c r="D14" t="s">
+        <v>202</v>
+      </c>
+      <c r="E14" t="s">
+        <v>266</v>
+      </c>
+      <c r="F14" t="s">
+        <v>267</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>269</v>
+      </c>
+      <c r="B15" t="s">
+        <v>270</v>
+      </c>
+      <c r="C15" t="s">
+        <v>271</v>
+      </c>
+      <c r="D15" t="s">
+        <v>202</v>
+      </c>
+      <c r="E15" t="s">
+        <v>272</v>
+      </c>
+      <c r="F15" t="s">
+        <v>273</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>275</v>
+      </c>
+      <c r="B16" t="s">
+        <v>276</v>
+      </c>
+      <c r="C16" t="s">
+        <v>239</v>
+      </c>
+      <c r="D16" t="s">
+        <v>202</v>
+      </c>
+      <c r="E16" t="s">
+        <v>277</v>
+      </c>
+      <c r="F16" t="s">
+        <v>278</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>280</v>
+      </c>
+      <c r="B17" t="s">
+        <v>281</v>
+      </c>
+      <c r="C17" t="s">
+        <v>282</v>
+      </c>
+      <c r="D17" t="s">
+        <v>202</v>
+      </c>
+      <c r="E17" t="s">
+        <v>283</v>
+      </c>
+      <c r="F17" t="s">
+        <v>284</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>286</v>
+      </c>
+      <c r="B18" t="s">
+        <v>287</v>
+      </c>
+      <c r="C18" t="s">
+        <v>288</v>
+      </c>
+      <c r="D18" t="s">
+        <v>289</v>
+      </c>
+      <c r="E18" t="s">
+        <v>290</v>
+      </c>
+      <c r="F18" t="s">
+        <v>284</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>292</v>
+      </c>
+      <c r="B19" t="s">
+        <v>293</v>
+      </c>
+      <c r="C19" t="s">
+        <v>294</v>
+      </c>
+      <c r="D19" t="s">
+        <v>202</v>
+      </c>
+      <c r="E19" t="s">
+        <v>295</v>
+      </c>
+      <c r="F19" t="s">
+        <v>296</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>298</v>
+      </c>
+      <c r="B20" t="s">
+        <v>299</v>
+      </c>
+      <c r="C20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D20" t="s">
+        <v>202</v>
+      </c>
+      <c r="E20" t="s">
+        <v>301</v>
+      </c>
+      <c r="F20" t="s">
+        <v>302</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>304</v>
+      </c>
+      <c r="B21" t="s">
+        <v>305</v>
+      </c>
+      <c r="C21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" t="s">
+        <v>202</v>
+      </c>
+      <c r="E21" t="s">
+        <v>306</v>
+      </c>
+      <c r="F21" t="s">
+        <v>307</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>309</v>
+      </c>
+      <c r="B22" t="s">
+        <v>310</v>
+      </c>
+      <c r="C22" t="s">
+        <v>311</v>
+      </c>
+      <c r="D22" t="s">
+        <v>202</v>
+      </c>
+      <c r="E22" t="s">
+        <v>312</v>
+      </c>
+      <c r="F22" t="s">
+        <v>313</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>309</v>
+      </c>
+      <c r="B23" t="s">
+        <v>315</v>
+      </c>
+      <c r="C23" t="s">
+        <v>239</v>
+      </c>
+      <c r="D23" t="s">
+        <v>209</v>
+      </c>
+      <c r="E23" t="s">
+        <v>316</v>
+      </c>
+      <c r="F23" t="s">
+        <v>317</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>319</v>
+      </c>
+      <c r="B24" t="s">
+        <v>320</v>
+      </c>
+      <c r="C24" t="s">
+        <v>321</v>
+      </c>
+      <c r="D24" t="s">
+        <v>202</v>
+      </c>
+      <c r="E24" t="s">
+        <v>322</v>
+      </c>
+      <c r="F24" t="s">
+        <v>323</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>325</v>
+      </c>
+      <c r="B25" t="s">
+        <v>326</v>
+      </c>
+      <c r="C25" t="s">
+        <v>327</v>
+      </c>
+      <c r="D25" t="s">
+        <v>202</v>
+      </c>
+      <c r="E25" t="s">
+        <v>328</v>
+      </c>
+      <c r="F25" t="s">
+        <v>329</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>331</v>
+      </c>
+      <c r="B26" t="s">
+        <v>332</v>
+      </c>
+      <c r="C26" t="s">
+        <v>333</v>
+      </c>
+      <c r="D26" t="s">
+        <v>202</v>
+      </c>
+      <c r="E26" t="s">
+        <v>334</v>
+      </c>
+      <c r="F26" t="s">
+        <v>335</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>331</v>
+      </c>
+      <c r="B27" t="s">
+        <v>337</v>
+      </c>
+      <c r="C27" t="s">
+        <v>338</v>
+      </c>
+      <c r="D27" t="s">
+        <v>202</v>
+      </c>
+      <c r="E27" t="s">
+        <v>339</v>
+      </c>
+      <c r="F27" t="s">
+        <v>340</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>342</v>
+      </c>
+      <c r="B28" t="s">
+        <v>343</v>
+      </c>
+      <c r="C28" t="s">
+        <v>265</v>
+      </c>
+      <c r="D28" t="s">
+        <v>202</v>
+      </c>
+      <c r="E28" t="s">
+        <v>344</v>
+      </c>
+      <c r="F28" t="s">
+        <v>273</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>346</v>
+      </c>
+      <c r="B29" t="s">
+        <v>347</v>
+      </c>
+      <c r="C29" t="s">
+        <v>239</v>
+      </c>
+      <c r="D29" t="s">
+        <v>202</v>
+      </c>
+      <c r="E29" t="s">
+        <v>348</v>
+      </c>
+      <c r="F29" t="s">
+        <v>273</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>350</v>
+      </c>
+      <c r="B30" t="s">
+        <v>351</v>
+      </c>
+      <c r="C30" t="s">
+        <v>352</v>
+      </c>
+      <c r="D30" t="s">
+        <v>202</v>
+      </c>
+      <c r="E30" t="s">
+        <v>353</v>
+      </c>
+      <c r="F30" t="s">
+        <v>354</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>356</v>
+      </c>
+      <c r="B31" t="s">
+        <v>357</v>
+      </c>
+      <c r="C31" t="s">
+        <v>300</v>
+      </c>
+      <c r="D31" t="s">
+        <v>202</v>
+      </c>
+      <c r="E31" t="s">
+        <v>358</v>
+      </c>
+      <c r="F31" t="s">
+        <v>359</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>361</v>
+      </c>
+      <c r="B32" t="s">
+        <v>362</v>
+      </c>
+      <c r="C32" t="s">
+        <v>363</v>
+      </c>
+      <c r="D32" t="s">
+        <v>202</v>
+      </c>
+      <c r="E32" t="s">
+        <v>364</v>
+      </c>
+      <c r="F32" t="s">
+        <v>222</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>366</v>
+      </c>
+      <c r="B33" t="s">
+        <v>367</v>
+      </c>
+      <c r="C33" t="s">
+        <v>265</v>
+      </c>
+      <c r="D33" t="s">
+        <v>202</v>
+      </c>
+      <c r="E33" t="s">
+        <v>368</v>
+      </c>
+      <c r="F33" t="s">
+        <v>369</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>371</v>
+      </c>
+      <c r="B34" t="s">
+        <v>372</v>
+      </c>
+      <c r="C34" t="s">
+        <v>373</v>
+      </c>
+      <c r="D34" t="s">
+        <v>202</v>
+      </c>
+      <c r="E34" t="s">
+        <v>222</v>
+      </c>
+      <c r="F34" t="s">
+        <v>374</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>376</v>
+      </c>
+      <c r="B35" t="s">
+        <v>293</v>
+      </c>
+      <c r="C35" t="s">
+        <v>294</v>
+      </c>
+      <c r="D35" t="s">
+        <v>202</v>
+      </c>
+      <c r="E35" t="s">
+        <v>377</v>
+      </c>
+      <c r="F35" t="s">
+        <v>296</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>379</v>
+      </c>
+      <c r="B36" t="s">
+        <v>380</v>
+      </c>
+      <c r="C36" t="s">
+        <v>321</v>
+      </c>
+      <c r="D36" t="s">
+        <v>202</v>
+      </c>
+      <c r="E36" t="s">
+        <v>381</v>
+      </c>
+      <c r="F36" t="s">
+        <v>382</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>384</v>
+      </c>
+      <c r="B37" t="s">
+        <v>293</v>
+      </c>
+      <c r="C37" t="s">
+        <v>294</v>
+      </c>
+      <c r="D37" t="s">
+        <v>202</v>
+      </c>
+      <c r="E37" t="s">
+        <v>377</v>
+      </c>
+      <c r="F37" t="s">
+        <v>296</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>386</v>
+      </c>
+      <c r="B38" t="s">
+        <v>387</v>
+      </c>
+      <c r="C38" t="s">
+        <v>388</v>
+      </c>
+      <c r="D38" t="s">
+        <v>202</v>
+      </c>
+      <c r="E38" t="s">
+        <v>389</v>
+      </c>
+      <c r="F38" t="s">
+        <v>390</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>392</v>
+      </c>
+      <c r="B39" t="s">
+        <v>299</v>
+      </c>
+      <c r="C39" t="s">
+        <v>300</v>
+      </c>
+      <c r="D39" t="s">
+        <v>202</v>
+      </c>
+      <c r="E39" t="s">
+        <v>393</v>
+      </c>
+      <c r="F39" t="s">
+        <v>302</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>395</v>
+      </c>
+      <c r="B40" t="s">
+        <v>299</v>
+      </c>
+      <c r="C40" t="s">
+        <v>300</v>
+      </c>
+      <c r="D40" t="s">
+        <v>202</v>
+      </c>
+      <c r="E40" t="s">
+        <v>328</v>
+      </c>
+      <c r="F40" t="s">
+        <v>396</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>398</v>
+      </c>
+      <c r="B41" t="s">
+        <v>399</v>
+      </c>
+      <c r="C41" t="s">
+        <v>400</v>
+      </c>
+      <c r="D41" t="s">
+        <v>202</v>
+      </c>
+      <c r="E41" t="s">
+        <v>401</v>
+      </c>
+      <c r="F41" t="s">
+        <v>402</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>404</v>
+      </c>
+      <c r="B42" t="s">
+        <v>405</v>
+      </c>
+      <c r="C42" t="s">
+        <v>406</v>
+      </c>
+      <c r="D42" t="s">
+        <v>202</v>
+      </c>
+      <c r="E42" t="s">
+        <v>407</v>
+      </c>
+      <c r="F42" t="s">
+        <v>408</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>410</v>
+      </c>
+      <c r="B43" t="s">
+        <v>411</v>
+      </c>
+      <c r="C43" t="s">
+        <v>412</v>
+      </c>
+      <c r="D43" t="s">
+        <v>202</v>
+      </c>
+      <c r="E43" t="s">
+        <v>413</v>
+      </c>
+      <c r="F43" t="s">
+        <v>414</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>416</v>
+      </c>
+      <c r="B44" t="s">
+        <v>417</v>
+      </c>
+      <c r="C44" t="s">
+        <v>239</v>
+      </c>
+      <c r="D44" t="s">
+        <v>202</v>
+      </c>
+      <c r="E44" t="s">
+        <v>277</v>
+      </c>
+      <c r="F44" t="s">
+        <v>222</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>419</v>
+      </c>
+      <c r="B45" t="s">
+        <v>299</v>
+      </c>
+      <c r="C45" t="s">
+        <v>300</v>
+      </c>
+      <c r="D45" t="s">
+        <v>202</v>
+      </c>
+      <c r="E45" t="s">
+        <v>420</v>
+      </c>
+      <c r="F45" t="s">
+        <v>302</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>422</v>
+      </c>
+      <c r="B46" t="s">
+        <v>423</v>
+      </c>
+      <c r="C46" t="s">
+        <v>265</v>
+      </c>
+      <c r="D46" t="s">
+        <v>202</v>
+      </c>
+      <c r="E46" t="s">
+        <v>245</v>
+      </c>
+      <c r="F46" t="s">
+        <v>424</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>426</v>
+      </c>
+      <c r="B47" t="s">
+        <v>427</v>
+      </c>
+      <c r="C47" t="s">
+        <v>428</v>
+      </c>
+      <c r="D47" t="s">
+        <v>202</v>
+      </c>
+      <c r="E47" t="s">
+        <v>429</v>
+      </c>
+      <c r="F47" t="s">
+        <v>430</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>432</v>
+      </c>
+      <c r="B48" t="s">
+        <v>433</v>
+      </c>
+      <c r="C48" t="s">
+        <v>400</v>
+      </c>
+      <c r="D48" t="s">
+        <v>202</v>
+      </c>
+      <c r="E48" t="s">
+        <v>434</v>
+      </c>
+      <c r="F48" t="s">
+        <v>435</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>437</v>
+      </c>
+      <c r="B49" t="s">
+        <v>438</v>
+      </c>
+      <c r="C49" t="s">
+        <v>439</v>
+      </c>
+      <c r="D49" t="s">
+        <v>202</v>
+      </c>
+      <c r="E49" t="s">
+        <v>440</v>
+      </c>
+      <c r="F49" t="s">
+        <v>441</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>443</v>
+      </c>
+      <c r="B50" t="s">
+        <v>444</v>
+      </c>
+      <c r="C50" t="s">
+        <v>239</v>
+      </c>
+      <c r="D50" t="s">
+        <v>202</v>
+      </c>
+      <c r="E50" t="s">
+        <v>445</v>
+      </c>
+      <c r="F50" t="s">
+        <v>222</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>447</v>
+      </c>
+      <c r="B51" t="s">
+        <v>448</v>
+      </c>
+      <c r="C51" t="s">
+        <v>449</v>
+      </c>
+      <c r="D51" t="s">
+        <v>202</v>
+      </c>
+      <c r="E51" t="s">
+        <v>450</v>
+      </c>
+      <c r="F51" t="s">
+        <v>451</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>453</v>
+      </c>
+      <c r="B52" t="s">
+        <v>226</v>
+      </c>
+      <c r="C52" t="s">
+        <v>227</v>
+      </c>
+      <c r="D52" t="s">
+        <v>202</v>
+      </c>
+      <c r="E52" t="s">
+        <v>228</v>
+      </c>
+      <c r="F52" t="s">
+        <v>229</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>455</v>
+      </c>
+      <c r="B53" t="s">
+        <v>456</v>
+      </c>
+      <c r="C53" t="s">
+        <v>457</v>
+      </c>
+      <c r="D53" t="s">
+        <v>202</v>
+      </c>
+      <c r="E53" t="s">
+        <v>458</v>
+      </c>
+      <c r="F53" t="s">
+        <v>459</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>461</v>
+      </c>
+      <c r="B54" t="s">
+        <v>462</v>
+      </c>
+      <c r="C54" t="s">
+        <v>463</v>
+      </c>
+      <c r="D54" t="s">
+        <v>202</v>
+      </c>
+      <c r="E54" t="s">
+        <v>464</v>
+      </c>
+      <c r="F54" t="s">
+        <v>465</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>467</v>
+      </c>
+      <c r="B55" t="s">
+        <v>456</v>
+      </c>
+      <c r="C55" t="s">
+        <v>468</v>
+      </c>
+      <c r="D55" t="s">
+        <v>202</v>
+      </c>
+      <c r="E55" t="s">
+        <v>469</v>
+      </c>
+      <c r="F55" t="s">
+        <v>459</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>471</v>
+      </c>
+      <c r="B56" t="s">
+        <v>472</v>
+      </c>
+      <c r="C56" t="s">
+        <v>400</v>
+      </c>
+      <c r="D56" t="s">
+        <v>209</v>
+      </c>
+      <c r="E56" t="s">
+        <v>473</v>
+      </c>
+      <c r="F56" t="s">
+        <v>204</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>475</v>
+      </c>
+      <c r="B57" t="s">
+        <v>476</v>
+      </c>
+      <c r="C57" t="s">
+        <v>400</v>
+      </c>
+      <c r="D57" t="s">
+        <v>202</v>
+      </c>
+      <c r="E57" t="s">
+        <v>477</v>
+      </c>
+      <c r="F57" t="s">
+        <v>273</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>479</v>
+      </c>
+      <c r="B58" t="s">
+        <v>480</v>
+      </c>
+      <c r="C58" t="s">
+        <v>481</v>
+      </c>
+      <c r="D58" t="s">
+        <v>202</v>
+      </c>
+      <c r="E58" t="s">
+        <v>482</v>
+      </c>
+      <c r="F58" t="s">
+        <v>483</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>485</v>
+      </c>
+      <c r="B59" t="s">
+        <v>486</v>
+      </c>
+      <c r="C59" t="s">
+        <v>487</v>
+      </c>
+      <c r="D59" t="s">
+        <v>202</v>
+      </c>
+      <c r="E59" t="s">
+        <v>488</v>
+      </c>
+      <c r="F59" t="s">
+        <v>489</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>491</v>
+      </c>
+      <c r="B60" t="s">
+        <v>326</v>
+      </c>
+      <c r="C60" t="s">
+        <v>265</v>
+      </c>
+      <c r="D60" t="s">
+        <v>202</v>
+      </c>
+      <c r="E60" t="s">
+        <v>413</v>
+      </c>
+      <c r="F60" t="s">
+        <v>329</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>493</v>
+      </c>
+      <c r="B61" t="s">
+        <v>494</v>
+      </c>
+      <c r="C61" t="s">
+        <v>400</v>
+      </c>
+      <c r="D61" t="s">
+        <v>209</v>
+      </c>
+      <c r="E61" t="s">
+        <v>495</v>
+      </c>
+      <c r="F61" t="s">
+        <v>496</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>498</v>
+      </c>
+      <c r="B62" t="s">
+        <v>499</v>
+      </c>
+      <c r="C62" t="s">
+        <v>239</v>
+      </c>
+      <c r="D62" t="s">
+        <v>202</v>
+      </c>
+      <c r="E62" t="s">
+        <v>500</v>
+      </c>
+      <c r="F62" t="s">
+        <v>501</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>503</v>
+      </c>
+      <c r="B63" t="s">
+        <v>504</v>
+      </c>
+      <c r="C63" t="s">
+        <v>449</v>
+      </c>
+      <c r="D63" t="s">
+        <v>202</v>
+      </c>
+      <c r="E63" t="s">
+        <v>505</v>
+      </c>
+      <c r="F63" t="s">
+        <v>506</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>508</v>
+      </c>
+      <c r="B64" t="s">
+        <v>509</v>
+      </c>
+      <c r="C64" t="s">
+        <v>510</v>
+      </c>
+      <c r="D64" t="s">
+        <v>202</v>
+      </c>
+      <c r="E64" t="s">
+        <v>511</v>
+      </c>
+      <c r="F64" t="s">
+        <v>512</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>514</v>
+      </c>
+      <c r="B65" t="s">
+        <v>515</v>
+      </c>
+      <c r="C65" t="s">
+        <v>400</v>
+      </c>
+      <c r="D65" t="s">
+        <v>202</v>
+      </c>
+      <c r="E65" t="s">
+        <v>516</v>
+      </c>
+      <c r="F65" t="s">
+        <v>517</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>519</v>
+      </c>
+      <c r="B66" t="s">
+        <v>520</v>
+      </c>
+      <c r="C66" t="s">
+        <v>521</v>
+      </c>
+      <c r="D66" t="s">
+        <v>202</v>
+      </c>
+      <c r="E66" t="s">
+        <v>522</v>
+      </c>
+      <c r="F66" t="s">
+        <v>523</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>519</v>
+      </c>
+      <c r="B67" t="s">
+        <v>520</v>
+      </c>
+      <c r="C67" t="s">
+        <v>525</v>
+      </c>
+      <c r="D67" t="s">
+        <v>202</v>
+      </c>
+      <c r="E67" t="s">
+        <v>522</v>
+      </c>
+      <c r="F67" t="s">
+        <v>523</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>519</v>
+      </c>
+      <c r="B68" t="s">
+        <v>520</v>
+      </c>
+      <c r="C68" t="s">
+        <v>457</v>
+      </c>
+      <c r="D68" t="s">
+        <v>202</v>
+      </c>
+      <c r="E68" t="s">
+        <v>522</v>
+      </c>
+      <c r="F68" t="s">
+        <v>523</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>528</v>
+      </c>
+      <c r="B69" t="s">
+        <v>529</v>
+      </c>
+      <c r="C69" t="s">
+        <v>530</v>
+      </c>
+      <c r="D69" t="s">
+        <v>202</v>
+      </c>
+      <c r="E69" t="s">
+        <v>531</v>
+      </c>
+      <c r="F69" t="s">
+        <v>532</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>534</v>
+      </c>
+      <c r="B70" t="s">
+        <v>535</v>
+      </c>
+      <c r="C70" t="s">
+        <v>536</v>
+      </c>
+      <c r="D70" t="s">
+        <v>202</v>
+      </c>
+      <c r="E70" t="s">
+        <v>222</v>
+      </c>
+      <c r="F70" t="s">
+        <v>537</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>539</v>
+      </c>
+      <c r="B71" t="s">
+        <v>540</v>
+      </c>
+      <c r="C71" t="s">
+        <v>300</v>
+      </c>
+      <c r="D71" t="s">
+        <v>202</v>
+      </c>
+      <c r="E71" t="s">
+        <v>541</v>
+      </c>
+      <c r="F71" t="s">
+        <v>542</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>544</v>
+      </c>
+      <c r="B72" t="s">
+        <v>448</v>
+      </c>
+      <c r="C72" t="s">
+        <v>449</v>
+      </c>
+      <c r="D72" t="s">
+        <v>202</v>
+      </c>
+      <c r="E72" t="s">
+        <v>545</v>
+      </c>
+      <c r="F72" t="s">
+        <v>546</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>548</v>
+      </c>
+      <c r="B73" t="s">
+        <v>549</v>
+      </c>
+      <c r="C73" t="s">
+        <v>239</v>
+      </c>
+      <c r="D73" t="s">
+        <v>202</v>
+      </c>
+      <c r="E73" t="s">
+        <v>550</v>
+      </c>
+      <c r="F73" t="s">
+        <v>222</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>552</v>
+      </c>
+      <c r="B74" t="s">
+        <v>553</v>
+      </c>
+      <c r="C74" t="s">
+        <v>400</v>
+      </c>
+      <c r="D74" t="s">
+        <v>202</v>
+      </c>
+      <c r="E74" t="s">
+        <v>554</v>
+      </c>
+      <c r="F74" t="s">
+        <v>555</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>557</v>
+      </c>
+      <c r="B75" t="s">
+        <v>558</v>
+      </c>
+      <c r="C75" t="s">
+        <v>400</v>
+      </c>
+      <c r="D75" t="s">
+        <v>202</v>
+      </c>
+      <c r="E75" t="s">
+        <v>559</v>
+      </c>
+      <c r="F75" t="s">
+        <v>532</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>561</v>
+      </c>
+      <c r="B76" t="s">
+        <v>238</v>
+      </c>
+      <c r="C76" t="s">
+        <v>239</v>
+      </c>
+      <c r="D76" t="s">
+        <v>202</v>
+      </c>
+      <c r="E76" t="s">
+        <v>562</v>
+      </c>
+      <c r="F76" t="s">
+        <v>241</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>564</v>
+      </c>
+      <c r="B77" t="s">
+        <v>565</v>
+      </c>
+      <c r="C77" t="s">
+        <v>352</v>
+      </c>
+      <c r="D77" t="s">
+        <v>202</v>
+      </c>
+      <c r="E77" t="s">
+        <v>566</v>
+      </c>
+      <c r="F77" t="s">
+        <v>567</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>569</v>
+      </c>
+      <c r="B78" t="s">
+        <v>570</v>
+      </c>
+      <c r="C78" t="s">
+        <v>571</v>
+      </c>
+      <c r="D78" t="s">
+        <v>202</v>
+      </c>
+      <c r="E78" t="s">
+        <v>572</v>
+      </c>
+      <c r="F78" t="s">
+        <v>573</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>575</v>
+      </c>
+      <c r="B79" t="s">
+        <v>576</v>
+      </c>
+      <c r="C79" t="s">
+        <v>577</v>
+      </c>
+      <c r="D79" t="s">
+        <v>202</v>
+      </c>
+      <c r="E79" t="s">
+        <v>578</v>
+      </c>
+      <c r="F79" t="s">
+        <v>222</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>580</v>
+      </c>
+      <c r="B80" t="s">
+        <v>581</v>
+      </c>
+      <c r="C80" t="s">
+        <v>582</v>
+      </c>
+      <c r="D80" t="s">
+        <v>202</v>
+      </c>
+      <c r="E80" t="s">
+        <v>583</v>
+      </c>
+      <c r="F80" t="s">
+        <v>584</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>586</v>
+      </c>
+      <c r="B81" t="s">
+        <v>293</v>
+      </c>
+      <c r="C81" t="s">
+        <v>294</v>
+      </c>
+      <c r="D81" t="s">
+        <v>202</v>
+      </c>
+      <c r="E81" t="s">
+        <v>587</v>
+      </c>
+      <c r="F81" t="s">
+        <v>296</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>589</v>
+      </c>
+      <c r="B82" t="s">
+        <v>590</v>
+      </c>
+      <c r="C82" t="s">
+        <v>400</v>
+      </c>
+      <c r="D82" t="s">
+        <v>202</v>
+      </c>
+      <c r="E82" t="s">
+        <v>591</v>
+      </c>
+      <c r="F82" t="s">
+        <v>592</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>594</v>
+      </c>
+      <c r="B83" t="s">
+        <v>595</v>
+      </c>
+      <c r="C83" t="s">
+        <v>596</v>
+      </c>
+      <c r="D83" t="s">
+        <v>202</v>
+      </c>
+      <c r="E83" t="s">
+        <v>364</v>
+      </c>
+      <c r="F83" t="s">
+        <v>597</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>599</v>
+      </c>
+      <c r="B84" t="s">
+        <v>238</v>
+      </c>
+      <c r="C84" t="s">
+        <v>239</v>
+      </c>
+      <c r="D84" t="s">
+        <v>202</v>
+      </c>
+      <c r="E84" t="s">
+        <v>339</v>
+      </c>
+      <c r="F84" t="s">
+        <v>241</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>601</v>
+      </c>
+      <c r="B85" t="s">
+        <v>602</v>
+      </c>
+      <c r="C85" t="s">
+        <v>239</v>
+      </c>
+      <c r="D85" t="s">
+        <v>202</v>
+      </c>
+      <c r="E85" t="s">
+        <v>603</v>
+      </c>
+      <c r="F85" t="s">
+        <v>222</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>605</v>
+      </c>
+      <c r="B86" t="s">
+        <v>606</v>
+      </c>
+      <c r="C86" t="s">
+        <v>607</v>
+      </c>
+      <c r="D86" t="s">
+        <v>209</v>
+      </c>
+      <c r="E86" t="s">
+        <v>608</v>
+      </c>
+      <c r="F86" t="s">
+        <v>592</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>609</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-10-26.xlsx
+++ b/docs/xlsx/jobs-2026-10-26.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="807">
   <si>
     <t>Title</t>
   </si>
@@ -577,6 +577,39 @@
     <t>https://www.conservationjobboard.com/job-listing-youth--community-programs-manager-lakewood-colorado/4153225414</t>
   </si>
   <si>
+    <t>Associate Director of Brand &amp; Digital Strategy</t>
+  </si>
+  <si>
+    <t>Western Resource Advocates (WRA)</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t>100,000 and above</t>
+  </si>
+  <si>
+    <t>Sustainability</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/associate-director-of-brand-digital-strategy/</t>
+  </si>
+  <si>
+    <t>Digital Engagement Specialist</t>
+  </si>
+  <si>
+    <t>60,000 - 80,000</t>
+  </si>
+  <si>
+    <t>Conservation</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/digital-engagement-specialist-2/</t>
+  </si>
+  <si>
     <t>Senior Construction Project Manager</t>
   </si>
   <si>
@@ -586,12 +619,6 @@
     <t>Portland, Oregon, United States</t>
   </si>
   <si>
-    <t>Full-Time</t>
-  </si>
-  <si>
-    <t>100,000 and above</t>
-  </si>
-  <si>
     <t>Green Building</t>
   </si>
   <si>
@@ -673,6 +700,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/a5031cc3ea49413dac42af589052ac93-administrative-assistant-onsite-our-place-of-new-trier-wilmette</t>
   </si>
   <si>
+    <t>Advancement Director, Tennessee and Kentucky Chapter</t>
+  </si>
+  <si>
+    <t>Parkinson's Foundation</t>
+  </si>
+  <si>
+    <t>Remote (Tennessee)</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eb18524f39834c0784a82e20326017d0-advancement-director-tennessee-and-kentucky-chapter-parkinsons-foundation-miami</t>
+  </si>
+  <si>
     <t>Agroflorestor(a)</t>
   </si>
   <si>
@@ -709,6 +754,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/7b08f41f67c748a282a96e86886ee5b7-anti-trafficking-services-caseworker-preble-street-portland</t>
   </si>
   <si>
+    <t>Anti-Trafficking Services Minors Caseworker</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/202578df1fa3467db158dd21263f0b54-anti-trafficking-services-minors-caseworker-preble-street-portland</t>
+  </si>
+  <si>
     <t>Anti-Trafficking Services Outreach Specialist</t>
   </si>
   <si>
@@ -727,6 +778,33 @@
     <t>https://www.idealist.org/en/job/bd6ab565a98a466c865be0f5c1ce0ca5-assistant-associate-or-full-professor-in-community-psychology-the-american-university-in-cairo-hewlett</t>
   </si>
   <si>
+    <t>Western Resource Advocates</t>
+  </si>
+  <si>
+    <t>Boulder, CO</t>
+  </si>
+  <si>
+    <t>USD 97750.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e9f4d7ef35004c04a3406c64697c5c2b-associate-director-of-brand-digital-strategy-western-resource-advocates-boulder</t>
+  </si>
+  <si>
+    <t>Associate Director, Pro-Vaccine Legal Alliance</t>
+  </si>
+  <si>
+    <t>American Families for Vaccines</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e6a8dab9bc224be38a2871e9455f823b-associate-director-pro-vaccine-legal-alliance-american-families-for-vaccines-portland</t>
+  </si>
+  <si>
     <t>Associate Supervising/Supervising Attorney</t>
   </si>
   <si>
@@ -745,6 +823,60 @@
     <t>https://www.idealist.org/en/nonprofit-job/00ac658fa0a6473693405df2365938c5-associate-supervisingsupervising-attorney-unlocal-inc-new-york</t>
   </si>
   <si>
+    <t>Associate Vice President, Major Gifts</t>
+  </si>
+  <si>
+    <t>Lucile Packard Foundation for Children's Health</t>
+  </si>
+  <si>
+    <t>Palo Alto, CA</t>
+  </si>
+  <si>
+    <t>USD 250000.00 - 270000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d21ecef6729649c3b39425820f74b61a-associate-vice-president-major-gifts-lucile-packard-foundation-for-childrens-health-palo-alto</t>
+  </si>
+  <si>
+    <t>Attorney</t>
+  </si>
+  <si>
+    <t>Act - Advocates for Community Transformation</t>
+  </si>
+  <si>
+    <t>Fort Worth, Texas</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Crime Safety, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5bad5698007a452d8d4c953d35dd7766-attorney-act-advocates-for-community-transformation-fort-worth</t>
+  </si>
+  <si>
+    <t>BLACK RURAL ORGANIZER–IN-TRAINING - Pacific Region (CA, NV, UT, CO, AZ), Northwest Region (NM &amp; WA, OR, ID, MT, WY), &amp; Northern Plains (ND,SD,NE,KS,IA,MN)</t>
+  </si>
+  <si>
+    <t>The Chisholm Legacy Project: A Resource Hub for Black Frontline Climate Justice Leadership</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fd7a46fe939c47de96f9127b98669ad8-black-rural-organizerin-training-pacific-region-ca-nv-ut-co-az-northwest-region-nm-wa-or-id-mt-wy-northern-plains-ndsdneksiamn-the-chisholm-legacy-project-a-resource-hub-for-black-frontline-climate-justice-leadership-allensworth</t>
+  </si>
+  <si>
     <t>Business Development Associate</t>
   </si>
   <si>
@@ -772,6 +904,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/77ac6e62c4094b979064f9ce95edb556-business-support-assistant-to-the-deputy-regional-director-world-food-programme-panama-city</t>
   </si>
   <si>
+    <t>CAA Director of Giving</t>
+  </si>
+  <si>
+    <t>Asian Americans for Civil Rights and Equality (AACRE)</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 149000.00 - 155000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a318e30390a6435d86d11430925c6cb9-caa-director-of-giving-asian-americans-for-civil-rights-and-equality-aacre-san-francisco</t>
+  </si>
+  <si>
     <t>Case Supervisor and Volunteer Recruiter</t>
   </si>
   <si>
@@ -805,6 +955,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/ab3a44b24a224e22a1697a40d65619bf-chief-advancement-officer-lowcountry-land-trust-charleston</t>
   </si>
   <si>
+    <t>Chief Executive Officer</t>
+  </si>
+  <si>
+    <t>RCF Connects (Richmond Community Foundation)</t>
+  </si>
+  <si>
+    <t>Richmond, California</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 180000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3ed1e0344b844df98bf58670b72af645-chief-executive-officer-rcf-connects-richmond-community-foundation-richmond</t>
+  </si>
+  <si>
     <t>Chief Financial Officer, ABCD</t>
   </si>
   <si>
@@ -841,21 +1009,51 @@
     <t>https://www.idealist.org/en/nonprofit-job/5bb309c0b889433b9f2676a6751190b3-chief-of-schools-colorado-schools-fund-denver</t>
   </si>
   <si>
+    <t>Colorado Education Program Coordinator</t>
+  </si>
+  <si>
+    <t>Ocean First Institute</t>
+  </si>
+  <si>
+    <t>Boulder, Colorado</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/32a9828055b74fbf803401ab48f9953e-colorado-education-program-coordinator-ocean-first-institute-boulder</t>
+  </si>
+  <si>
     <t>Communications Director</t>
   </si>
   <si>
     <t>The Explorers Club</t>
   </si>
   <si>
-    <t>USD 75000.00 - 85000.00/year</t>
-  </si>
-  <si>
     <t>Environment, Research Social Science</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/6b08b9e1ba94458a87284eb3ec573b8d-communications-director-the-explorers-club-new-york</t>
   </si>
   <si>
+    <t>Communications Manager</t>
+  </si>
+  <si>
+    <t>Foundation for Louisiana</t>
+  </si>
+  <si>
+    <t>Remote (Louisiana)</t>
+  </si>
+  <si>
+    <t>USD 61000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/098b56c309274fcf8057d3e38f80a451-communications-manager-foundation-for-louisiana-new-orleans</t>
+  </si>
+  <si>
     <t>Communities Program Associate</t>
   </si>
   <si>
@@ -868,9 +1066,6 @@
     <t>USD 52000.00 - 62000.00/year</t>
   </si>
   <si>
-    <t>Environment</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/68cc6988c43741baa1d396ef54790bd2-communities-program-associate-great-plains-institute-minneapolis</t>
   </si>
   <si>
@@ -892,6 +1087,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/5e0206d5d2b74d1b85d402df9afaec8b-community-liaison-ecology-center-ann-arbor-ann-arbor</t>
   </si>
   <si>
+    <t>Contracts and Compliance Specialist</t>
+  </si>
+  <si>
+    <t>Food Lifeline</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a8d545d4f8424baf95113b3fb8dcc240-contracts-and-compliance-specialist-food-lifeline-seattle</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>Pasadena Community Foundation</t>
+  </si>
+  <si>
+    <t>Pasadena, California</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Education, Disaster Relief</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f765305d9eb440e19ec6f3c58fe423a8-controller-pasadena-community-foundation-pasadena</t>
+  </si>
+  <si>
     <t>Controller (Director Level)</t>
   </si>
   <si>
@@ -901,9 +1132,6 @@
     <t>Remote (Los Angeles, California)</t>
   </si>
   <si>
-    <t>USD 120000.00 - 140000.00/year</t>
-  </si>
-  <si>
     <t>Education, Lgbtq</t>
   </si>
   <si>
@@ -928,6 +1156,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/6fac334154fb46efb08bde6b69c442ea-cook-ii-central-union-mission-washington</t>
   </si>
   <si>
+    <t>Corporate Engagement Manager</t>
+  </si>
+  <si>
+    <t>Truckers Against Trafficking</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/80cc079ea1ac48ad8d5171476cf19cdf-corporate-engagement-manager-truckers-against-trafficking-englewood</t>
+  </si>
+  <si>
     <t>Data and Policy Analyst</t>
   </si>
   <si>
@@ -982,15 +1222,27 @@
     <t>Raleigh, North Carolina</t>
   </si>
   <si>
-    <t>USD 85000.00 - 95000.00/year</t>
-  </si>
-  <si>
     <t>Arts Music, Education, Health Medicine</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/consultant-job/2960fb5b108d46019ff1e42c82586456-development-and-strategic-partnerships-manager-nc-rural-center-armstrong-mcguire-associates-raleigh</t>
   </si>
   <si>
+    <t>Development Coordinator – New Jersey Pennsylvania Chapter</t>
+  </si>
+  <si>
+    <t>Remote (New Jersey)</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ad5afa8c137743c597400eaf5efb8391-development-coordinator-new-jersey-pennsylvania-chapter-parkinsons-foundation-miami</t>
+  </si>
+  <si>
     <t>Development Coordinator, East Region</t>
   </si>
   <si>
@@ -1015,9 +1267,6 @@
     <t>Dairy Arts Center</t>
   </si>
   <si>
-    <t>Boulder, Colorado</t>
-  </si>
-  <si>
     <t>USD 85000.00 - 110000.00/year</t>
   </si>
   <si>
@@ -1054,6 +1303,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/dc2100117493419c948e438688283d33-development-director-boston-uncf-boston</t>
   </si>
   <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>The Gray Matter Experience</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/17d461061a5545c1b563cf3f4eb8dd4f-development-manager-the-gray-matter-experience-chicago</t>
+  </si>
+  <si>
+    <t>Remote (Colorado)</t>
+  </si>
+  <si>
+    <t>USD 62458.00 - 73480.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/72557e0bfe654431af6ee698f2870f47-digital-engagement-specialist-western-resource-advocates-boulder</t>
+  </si>
+  <si>
     <t>Director of Development</t>
   </si>
   <si>
@@ -1084,6 +1360,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/39de093d9a4b4a9abd45a5bb304e4174-director-of-fund-development-the-salvation-army-national-headquarters-alexandria</t>
   </si>
   <si>
+    <t>Director of Industry Outreach (Trucking)</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/78564528af724b33ada48aedba282e41-director-of-industry-outreach-trucking-truckers-against-trafficking-englewood</t>
+  </si>
+  <si>
     <t>Director of Membership and Marketing</t>
   </si>
   <si>
@@ -1144,6 +1429,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/eea78e2602e34e3aba04b255959d15ad-director-of-retreats-loretto-community-loretto-motherhouse-loretto</t>
   </si>
   <si>
+    <t>Director of Technology</t>
+  </si>
+  <si>
+    <t>The Water Project, Inc.</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b6254143b80e49fba916b13cd30c1791-director-of-technology-the-water-project-inc-concord</t>
+  </si>
+  <si>
     <t>Director, Development Operations</t>
   </si>
   <si>
@@ -1201,6 +1501,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/39e4f6dc91b84e6088004e8c9ded363f-driver-central-union-mission-washington</t>
   </si>
   <si>
+    <t>Early College Awareness College Access Program Specialist</t>
+  </si>
+  <si>
+    <t>CollegeBound Foundation</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 56000.00 - 61000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/27ea554161a24e1aa14f608d75d8f267-early-college-awareness-college-access-program-specialist-collegebound-foundation-baltimore</t>
+  </si>
+  <si>
     <t>Education and Employment Coordinator</t>
   </si>
   <si>
@@ -1216,9 +1534,6 @@
     <t>BrightFocus Foundation</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>USD 65000.00 - 75000.00/year</t>
   </si>
   <si>
@@ -1264,6 +1579,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/7daf35c63e8b4923a9a9556dfc4f2143-executive-director-multi-service-eating-disorders-association-newton</t>
   </si>
   <si>
+    <t>Executive Director-Treasurer</t>
+  </si>
+  <si>
+    <t>Massachusetts Teachers Association</t>
+  </si>
+  <si>
+    <t>Quincy, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 228000.00 - 253000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf5e1a72d1df41de97f5d2fa99feb908-executive-director-treasurer-massachusetts-teachers-association-quincy</t>
+  </si>
+  <si>
     <t>Executive Office Coordinator</t>
   </si>
   <si>
@@ -1276,9 +1606,6 @@
     <t>Facility Maintenance Manager</t>
   </si>
   <si>
-    <t>USD 60000.00 - 70000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/6e7ab7fe8c5c44cbb4f295e659015cf1-facility-maintenance-manager-central-union-mission-washington</t>
   </si>
   <si>
@@ -1363,9 +1690,6 @@
     <t>Access Living of Metropolitan Chicago</t>
   </si>
   <si>
-    <t>Chicago, Illinois</t>
-  </si>
-  <si>
     <t>USD 54500.00 - 59500.00/year</t>
   </si>
   <si>
@@ -1417,6 +1741,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/77bff999000846eabb1804c14fcd2c37-individual-and-major-giving-director-encore-community-services-new-york</t>
   </si>
   <si>
+    <t>Industry Outreach Specialist</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/110bc3b13c7c474994e4725a3641b189-industry-outreach-specialist-truckers-against-trafficking-englewood</t>
+  </si>
+  <si>
     <t>Inland Empire Education and Outreach Coordinator</t>
   </si>
   <si>
@@ -1441,6 +1774,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/f14ad49ed910427284f9825b2014ea67-institutional-giving-manager-grant-writer-dayenu-a-jewish-call-to-climate-action-new-york</t>
   </si>
   <si>
+    <t>Investment Partner</t>
+  </si>
+  <si>
+    <t>ica.fund</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 200000.00 - 240000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/34083202ef8140638299c98805ee4de6-investment-partner-icafund-oakland</t>
+  </si>
+  <si>
+    <t>Iraq Country Director</t>
+  </si>
+  <si>
+    <t>Free to Run</t>
+  </si>
+  <si>
+    <t>Erbil, Erbil Governorate, IQ</t>
+  </si>
+  <si>
+    <t>Education, Human Rights Civil Liberties, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6f12f078e2084e9597f0eefdafd5f50f-iraq-country-director-free-to-run-erbil</t>
+  </si>
+  <si>
     <t>Lead, Reviews (Math)</t>
   </si>
   <si>
@@ -1510,15 +1876,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/acc3a372c6e14af6a9f73511dfca5b3e-marketing-and-administrative-assistant-nu-haven-kapelye-hamden</t>
   </si>
   <si>
+    <t>Marketing Content Manager</t>
+  </si>
+  <si>
+    <t>Ballet Hispánico</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1f8764d3fa274cb0b03daf1c70be9786-marketing-content-manager-ballet-hispanico-new-york</t>
+  </si>
+  <si>
+    <t>Member Engagement Manager</t>
+  </si>
+  <si>
+    <t>Northern California Grantmakers</t>
+  </si>
+  <si>
+    <t>USD 90250.00 - 100225.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9dcaaf43f56242e39c9dabcddfcc8c2f-member-engagement-manager-northern-california-grantmakers-san-francisco</t>
+  </si>
+  <si>
+    <t>Northeast Director</t>
+  </si>
+  <si>
+    <t>Jobs to Move America</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 138000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Environment, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/707bce9285af4d6e9bd23fb7cfce046a-northeast-director-jobs-to-move-america-los-angeles</t>
+  </si>
+  <si>
     <t>OFFICE MANAGER/FRONT DESK</t>
   </si>
   <si>
     <t>IHI Therapy Center</t>
   </si>
   <si>
-    <t>USD 50000.00 - 50000.00/year</t>
-  </si>
-  <si>
     <t>Lgbtq, Mental Health</t>
   </si>
   <si>
@@ -1573,15 +1978,60 @@
     <t>https://www.idealist.org/en/nonprofit-job/25e2ba7b3dbc45fbb74cb99a08adb9c7-program-director-association-of-asian-american-investment-managers-san-francisco</t>
   </si>
   <si>
+    <t>Program Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/63b6f5e266ff450c8d9d2e8bc4d18906-program-manager-the-gray-matter-experience-chicago</t>
+  </si>
+  <si>
+    <t>ATLAS Fellows, Inc.</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Job Workplace, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2fda5a2473e5432eaa4b86ede07c4630-program-manager-atlas-fellows-inc-new-york</t>
+  </si>
+  <si>
+    <t>Program Manager, Network Convenings</t>
+  </si>
+  <si>
+    <t>Beyond100k</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b1f15f0d77014d03b991bb2d971294ad-program-manager-network-convenings-beyond100k-new-york</t>
+  </si>
+  <si>
+    <t>Program Operations Coordinator, Camden Food Fund</t>
+  </si>
+  <si>
+    <t>Community Foundation of South Jersey</t>
+  </si>
+  <si>
+    <t>Camden, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 32.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Hunger Food Security, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ecc63a055e144f80a71415e65a9e764e-program-operations-coordinator-camden-food-fund-community-foundation-of-south-jersey-camden</t>
+  </si>
+  <si>
     <t>Project Manager</t>
   </si>
   <si>
     <t>Immigrant Legal Resource Center</t>
   </si>
   <si>
-    <t>San Francisco, California</t>
-  </si>
-  <si>
     <t>USD 120574.50 - 129061.50/year</t>
   </si>
   <si>
@@ -1600,6 +2050,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/4dac40b0c4ec486fa2b241a9e0ba8b69-project-manager-immigrant-legal-resource-center-los-angeles</t>
   </si>
   <si>
+    <t>PUBLIC DEFENDER CLIENT ADVOCATE – Los Angeles, California HEAL PROGRAM</t>
+  </si>
+  <si>
+    <t>Partners for Justice</t>
+  </si>
+  <si>
+    <t>Long Beach, California</t>
+  </si>
+  <si>
+    <t>USD 52400.00 - 55980.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/159bb16894ef41d1895ce19d0b856244-public-defender-client-advocate-los-angeles-california-heal-program-partners-for-justice-long-beach</t>
+  </si>
+  <si>
     <t>Reach Out and Read Development Specialist, WA</t>
   </si>
   <si>
@@ -1612,12 +2080,27 @@
     <t>USD 70000.00 - 75000.00/year</t>
   </si>
   <si>
-    <t>Health Medicine</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/consultant-job/2b78b3bc7cdf4ba18b4c68c8c5a244e2-reach-out-and-read-development-specialist-wa-positively-partners-boston</t>
   </si>
   <si>
+    <t>Research &amp; Data Analyst, Age-Friendly Standards (STEM OPT, Full-Time or Part-Time)</t>
+  </si>
+  <si>
+    <t>American Association for Elder Care</t>
+  </si>
+  <si>
+    <t>Las Vegas, NV</t>
+  </si>
+  <si>
+    <t>USD 12.00 - 12.00/hour</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Health Medicine, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1c0cc697c3a94ea193cd0b746c53eba3-research-data-analyst-age-friendly-standards-stem-opt-full-time-or-part-time-american-association-for-elder-care-las-vegas</t>
+  </si>
+  <si>
     <t>Resource Protection Manager</t>
   </si>
   <si>
@@ -1660,6 +2143,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/9d2872875bca4801ac4027f74b618972-senior-development-associate-events-individual-giving-position-description-access-living-of-metropolitan-chicago-chicago</t>
   </si>
   <si>
+    <t>Senior Healing Justice Organizer</t>
+  </si>
+  <si>
+    <t>Restore Oakland</t>
+  </si>
+  <si>
+    <t>Community Development, Conflict Resolution, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d4eeac30dffa402ba164ecff9d0fa6cc-senior-healing-justice-organizer-restore-oakland-oakland</t>
+  </si>
+  <si>
     <t>Senior HRIS Analyst - Workday</t>
   </si>
   <si>
@@ -1717,12 +2212,18 @@
     <t>USD 140000.00 - 225000.00/year</t>
   </si>
   <si>
-    <t>Civic Engagement, Community Development, Economic Development</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/66d3facba9d04b3f95b06b3dd3bb2899-senior-vice-president-association-of-chamber-of-commerce-executives-alexandria</t>
   </si>
   <si>
+    <t>Senior Vice President of Institutional Advancement</t>
+  </si>
+  <si>
+    <t>St. Louis, Missouri</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/64690cfc6c0743238c0efbad5bb2590d-senior-vice-president-of-institutional-advancement-missouri-botanical-garden-st-louis</t>
+  </si>
+  <si>
     <t>Shelter Manager</t>
   </si>
   <si>
@@ -1774,6 +2275,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/c10e7c48067c46f8a5b648530dbf12db-special-education-teacher-2500-sign-on-bonus-saint-dominics-family-services-bronx</t>
   </si>
   <si>
+    <t>Sr. Director of Development</t>
+  </si>
+  <si>
+    <t>The Greenlining Institute</t>
+  </si>
+  <si>
+    <t>USD 133819.00 - 181202.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6b7a9619b4d242a6b50833a9c47b8f58-sr-director-of-development-the-greenlining-institute-oakland</t>
+  </si>
+  <si>
     <t>Sr. Director, Technology &amp; Systems</t>
   </si>
   <si>
@@ -1798,6 +2314,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/f4522350cd4d4d98a5473f5697722026-sr-manager-strategy-projects-special-initiatives-all-our-kin-new-haven</t>
   </si>
   <si>
+    <t>Staff Attorney-Compliance, Chief Legal Office/General Counsel's Office</t>
+  </si>
+  <si>
+    <t>Build Up Justice NYC (previously Brooklyn Legal Services Corporation A)</t>
+  </si>
+  <si>
+    <t>Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>USD 81600.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b46905c67a7c4652b0d1538add29dac9-staff-attorney-compliance-chief-legal-officegeneral-counsels-office-build-up-justice-nyc-previously-brooklyn-legal-services-corporation-a-brooklyn</t>
+  </si>
+  <si>
+    <t>Staff Attorney-Probono Coordinator, Chief Legal Office/General Counsel's Office</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6e6f5dd51a7c4495ad5c850e0ed11fd0-staff-attorney-probono-coordinator-chief-legal-officegeneral-counsels-office-build-up-justice-nyc-previously-brooklyn-legal-services-corporation-a-brooklyn</t>
+  </si>
+  <si>
     <t>Staff Attorney, Detention and Deportation Defense Initiative</t>
   </si>
   <si>
@@ -1807,9 +2347,6 @@
     <t>Newark, New Jersey</t>
   </si>
   <si>
-    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/2d2737bbd99a4274895cb3d7c45b777a-staff-attorney-detention-and-deportation-defense-initiative-afsc-american-friends-service-committee-newark</t>
   </si>
   <si>
@@ -1831,6 +2368,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/83bc43346f2f48eeb1d08a39198205f1-supervisor-case-management-wellness-together-university-settlement-society-of-new-york-new-york</t>
   </si>
   <si>
+    <t>Temporary Program Coordinator</t>
+  </si>
+  <si>
+    <t>Futures and Options</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 56000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ba2ba00b49d94fce85bf9bb773687ce2-temporary-program-coordinator-futures-and-options-new-york</t>
+  </si>
+  <si>
+    <t>Tenant Rights Advocacy Specialist</t>
+  </si>
+  <si>
+    <t>Inquilinos Unidos (United Tenants)</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>USD 32.00/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Immigrants Or Refugees, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a5afdfe8d478460ead21234f6c0cbdf3-tenant-rights-advocacy-specialist-inquilinos-unidos-united-tenants-los-angeles</t>
+  </si>
+  <si>
+    <t>Thrift Director</t>
+  </si>
+  <si>
+    <t>Beverly Bootstraps Community Services</t>
+  </si>
+  <si>
+    <t>Beverly, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6dd9ae4cd2724be4b9e84536b52dcbbb-thrift-director-beverly-bootstraps-community-services-beverly</t>
+  </si>
+  <si>
     <t>Tri-Lingual Comprehensive Domestic &amp; Sexual Violence Counselor/Advocate</t>
   </si>
   <si>
@@ -1844,6 +2429,12 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/99a68c725a65439dbead5c54ca92b5a4-tri-lingual-comprehensive-domestic-sexual-violence-counseloradvocate-independence-house-inc-barnstable</t>
+  </si>
+  <si>
+    <t>Youth on Transportation Program Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/18da9ef46d2148bb90e1861d73330623-youth-on-transportation-program-manager-truckers-against-trafficking-englewood</t>
   </si>
 </sst>
 </file>
@@ -3143,7 +3734,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3210,22 +3801,68 @@
         <v>194</v>
       </c>
       <c r="B3" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D3" t="s">
         <v>190</v>
       </c>
       <c r="E3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E4" t="s">
         <v>191</v>
       </c>
-      <c r="F3" t="s">
-        <v>197</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>198</v>
+      <c r="F4" t="s">
+        <v>201</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B5" t="s">
+        <v>204</v>
+      </c>
+      <c r="C5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F5" t="s">
+        <v>206</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -3233,6 +3870,8 @@
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3241,7 +3880,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3282,1957 +3921,2923 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B2" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="C2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E2" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="F2" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B3" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C3" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="D3" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="E3" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="F3" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="B4" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="C4" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="D4" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E4" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="F4" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B5" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C5" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="D5" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E5" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="F5" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B6" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="C6" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="D6" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E6" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="F6" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="B7" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="C7" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="D7" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E7" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="F7" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="B8" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C8" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="D8" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E8" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="F8" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B9" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C9" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D9" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E9" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F9" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B10" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="C10" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="D10" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E10" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="F10" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>247</v>
+        <v>187</v>
       </c>
       <c r="B11" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C11" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="D11" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E11" t="s">
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="F11" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="B12" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C12" t="s">
-        <v>254</v>
+        <v>189</v>
       </c>
       <c r="D12" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E12" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="F12" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B13" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C13" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D13" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E13" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F13" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B14" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C14" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D14" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E14" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="F14" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B15" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C15" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="D15" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E15" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F15" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B16" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C16" t="s">
-        <v>239</v>
+        <v>189</v>
       </c>
       <c r="D16" t="s">
-        <v>202</v>
+        <v>283</v>
       </c>
       <c r="E16" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="F16" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B17" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C17" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="D17" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E17" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="F17" t="s">
-        <v>284</v>
+        <v>237</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B18" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C18" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D18" t="s">
-        <v>289</v>
+        <v>211</v>
       </c>
       <c r="E18" t="s">
-        <v>290</v>
+        <v>237</v>
       </c>
       <c r="F18" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B19" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C19" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D19" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E19" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F19" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B20" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C20" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D20" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E20" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="F20" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B21" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>309</v>
       </c>
       <c r="D21" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E21" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F21" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B22" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C22" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D22" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E22" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F22" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="B23" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C23" t="s">
-        <v>239</v>
+        <v>321</v>
       </c>
       <c r="D23" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E23" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F23" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B24" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C24" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D24" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E24" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="F24" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B25" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C25" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="D25" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="E25" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="F25" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B26" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="C26" t="s">
-        <v>333</v>
+        <v>265</v>
       </c>
       <c r="D26" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E26" t="s">
-        <v>334</v>
+        <v>231</v>
       </c>
       <c r="F26" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="B27" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C27" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="D27" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E27" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="F27" t="s">
-        <v>340</v>
+        <v>317</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B28" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C28" t="s">
-        <v>265</v>
+        <v>348</v>
       </c>
       <c r="D28" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E28" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F28" t="s">
-        <v>273</v>
+        <v>335</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B29" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C29" t="s">
-        <v>239</v>
+        <v>353</v>
       </c>
       <c r="D29" t="s">
-        <v>202</v>
+        <v>354</v>
       </c>
       <c r="E29" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="F29" t="s">
-        <v>273</v>
+        <v>335</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B30" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C30" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="D30" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E30" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="F30" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B31" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="C31" t="s">
-        <v>300</v>
+        <v>365</v>
       </c>
       <c r="D31" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E31" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="F31" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="B32" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="C32" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="D32" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E32" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F32" t="s">
-        <v>222</v>
+        <v>372</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B33" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C33" t="s">
-        <v>265</v>
+        <v>376</v>
       </c>
       <c r="D33" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E33" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="F33" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="B34" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="C34" t="s">
-        <v>373</v>
+        <v>189</v>
       </c>
       <c r="D34" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E34" t="s">
-        <v>222</v>
+        <v>289</v>
       </c>
       <c r="F34" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="B35" t="s">
-        <v>293</v>
+        <v>385</v>
       </c>
       <c r="C35" t="s">
-        <v>294</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E35" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="F35" t="s">
-        <v>296</v>
+        <v>387</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B36" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="C36" t="s">
-        <v>321</v>
+        <v>391</v>
       </c>
       <c r="D36" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E36" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="F36" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B37" t="s">
-        <v>293</v>
+        <v>395</v>
       </c>
       <c r="C37" t="s">
-        <v>294</v>
+        <v>265</v>
       </c>
       <c r="D37" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="E37" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="F37" t="s">
-        <v>296</v>
+        <v>397</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="B38" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="C38" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="D38" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E38" t="s">
-        <v>389</v>
+        <v>360</v>
       </c>
       <c r="F38" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="B39" t="s">
-        <v>299</v>
+        <v>229</v>
       </c>
       <c r="C39" t="s">
-        <v>300</v>
+        <v>405</v>
       </c>
       <c r="D39" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E39" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="F39" t="s">
-        <v>302</v>
+        <v>407</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="B40" t="s">
-        <v>299</v>
+        <v>410</v>
       </c>
       <c r="C40" t="s">
-        <v>300</v>
+        <v>411</v>
       </c>
       <c r="D40" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E40" t="s">
-        <v>328</v>
+        <v>412</v>
       </c>
       <c r="F40" t="s">
-        <v>396</v>
+        <v>413</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>397</v>
+        <v>414</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="B41" t="s">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="C41" t="s">
-        <v>400</v>
+        <v>333</v>
       </c>
       <c r="D41" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E41" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="F41" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="B42" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="C42" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="D42" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E42" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="F42" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="B43" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="C43" t="s">
-        <v>412</v>
+        <v>321</v>
       </c>
       <c r="D43" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E43" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="F43" t="s">
-        <v>414</v>
+        <v>329</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="B44" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="C44" t="s">
-        <v>239</v>
+        <v>431</v>
       </c>
       <c r="D44" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E44" t="s">
-        <v>277</v>
+        <v>432</v>
       </c>
       <c r="F44" t="s">
-        <v>222</v>
+        <v>433</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>419</v>
+        <v>194</v>
       </c>
       <c r="B45" t="s">
-        <v>299</v>
+        <v>254</v>
       </c>
       <c r="C45" t="s">
-        <v>300</v>
+        <v>435</v>
       </c>
       <c r="D45" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E45" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="F45" t="s">
-        <v>302</v>
+        <v>257</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="C46" t="s">
         <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E46" t="s">
-        <v>245</v>
+        <v>440</v>
       </c>
       <c r="F46" t="s">
-        <v>424</v>
+        <v>329</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="B47" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="C47" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="D47" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E47" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="F47" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="B48" t="s">
-        <v>433</v>
+        <v>381</v>
       </c>
       <c r="C48" t="s">
-        <v>400</v>
+        <v>189</v>
       </c>
       <c r="D48" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E48" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="F48" t="s">
-        <v>435</v>
+        <v>382</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="B49" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="C49" t="s">
-        <v>439</v>
+        <v>376</v>
       </c>
       <c r="D49" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E49" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="F49" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="B50" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="C50" t="s">
-        <v>239</v>
+        <v>458</v>
       </c>
       <c r="D50" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E50" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="F50" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="B51" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="C51" t="s">
-        <v>449</v>
+        <v>321</v>
       </c>
       <c r="D51" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E51" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="F51" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="B52" t="s">
-        <v>226</v>
+        <v>467</v>
       </c>
       <c r="C52" t="s">
-        <v>227</v>
+        <v>468</v>
       </c>
       <c r="D52" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E52" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="F52" t="s">
-        <v>229</v>
+        <v>469</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="B53" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="C53" t="s">
-        <v>457</v>
+        <v>189</v>
       </c>
       <c r="D53" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E53" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="F53" t="s">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="B54" t="s">
-        <v>462</v>
+        <v>370</v>
       </c>
       <c r="C54" t="s">
-        <v>463</v>
+        <v>371</v>
       </c>
       <c r="D54" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E54" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="F54" t="s">
-        <v>465</v>
+        <v>372</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="B55" t="s">
-        <v>456</v>
+        <v>480</v>
       </c>
       <c r="C55" t="s">
-        <v>468</v>
+        <v>401</v>
       </c>
       <c r="D55" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E55" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="F55" t="s">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="B56" t="s">
-        <v>472</v>
+        <v>370</v>
       </c>
       <c r="C56" t="s">
-        <v>400</v>
+        <v>371</v>
       </c>
       <c r="D56" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E56" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F56" t="s">
-        <v>204</v>
+        <v>372</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="B57" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="C57" t="s">
-        <v>400</v>
+        <v>488</v>
       </c>
       <c r="D57" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E57" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="F57" t="s">
-        <v>273</v>
+        <v>490</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="B58" t="s">
-        <v>480</v>
+        <v>375</v>
       </c>
       <c r="C58" t="s">
-        <v>481</v>
+        <v>376</v>
       </c>
       <c r="D58" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E58" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="F58" t="s">
-        <v>483</v>
+        <v>378</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="B59" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="C59" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="D59" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E59" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="F59" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="B60" t="s">
-        <v>326</v>
+        <v>375</v>
       </c>
       <c r="C60" t="s">
-        <v>265</v>
+        <v>376</v>
       </c>
       <c r="D60" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E60" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F60" t="s">
-        <v>329</v>
+        <v>502</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="B61" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="C61" t="s">
-        <v>400</v>
+        <v>189</v>
       </c>
       <c r="D61" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E61" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="F61" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="B62" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="C62" t="s">
-        <v>239</v>
+        <v>511</v>
       </c>
       <c r="D62" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E62" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="F62" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="B63" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="C63" t="s">
-        <v>449</v>
+        <v>517</v>
       </c>
       <c r="D63" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E63" t="s">
-        <v>505</v>
+        <v>518</v>
       </c>
       <c r="F63" t="s">
-        <v>506</v>
+        <v>519</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>507</v>
+        <v>520</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="B64" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="C64" t="s">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="D64" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E64" t="s">
-        <v>511</v>
+        <v>524</v>
       </c>
       <c r="F64" t="s">
-        <v>512</v>
+        <v>329</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="B65" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="C65" t="s">
-        <v>400</v>
+        <v>265</v>
       </c>
       <c r="D65" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E65" t="s">
-        <v>516</v>
+        <v>231</v>
       </c>
       <c r="F65" t="s">
-        <v>517</v>
+        <v>237</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="B66" t="s">
-        <v>520</v>
+        <v>375</v>
       </c>
       <c r="C66" t="s">
-        <v>521</v>
+        <v>376</v>
       </c>
       <c r="D66" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E66" t="s">
-        <v>522</v>
+        <v>449</v>
       </c>
       <c r="F66" t="s">
-        <v>523</v>
+        <v>378</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="B67" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="C67" t="s">
-        <v>525</v>
+        <v>321</v>
       </c>
       <c r="D67" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E67" t="s">
-        <v>522</v>
+        <v>289</v>
       </c>
       <c r="F67" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="B68" t="s">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="C68" t="s">
-        <v>457</v>
+        <v>537</v>
       </c>
       <c r="D68" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E68" t="s">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="F68" t="s">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>527</v>
+        <v>540</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="B69" t="s">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="C69" t="s">
-        <v>530</v>
+        <v>189</v>
       </c>
       <c r="D69" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E69" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="F69" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="B70" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="C70" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="D70" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E70" t="s">
-        <v>222</v>
+        <v>549</v>
       </c>
       <c r="F70" t="s">
-        <v>537</v>
+        <v>550</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>538</v>
+        <v>551</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>539</v>
+        <v>552</v>
       </c>
       <c r="B71" t="s">
-        <v>540</v>
+        <v>553</v>
       </c>
       <c r="C71" t="s">
-        <v>300</v>
+        <v>265</v>
       </c>
       <c r="D71" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E71" t="s">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="F71" t="s">
-        <v>542</v>
+        <v>237</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B72" t="s">
-        <v>448</v>
+        <v>557</v>
       </c>
       <c r="C72" t="s">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="D72" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E72" t="s">
-        <v>545</v>
+        <v>558</v>
       </c>
       <c r="F72" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>547</v>
+        <v>560</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>548</v>
+        <v>561</v>
       </c>
       <c r="B73" t="s">
-        <v>549</v>
+        <v>241</v>
       </c>
       <c r="C73" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D73" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E73" t="s">
-        <v>550</v>
+        <v>243</v>
       </c>
       <c r="F73" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>551</v>
+        <v>562</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="B74" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="C74" t="s">
-        <v>400</v>
+        <v>565</v>
       </c>
       <c r="D74" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E74" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="F74" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="B75" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="C75" t="s">
-        <v>400</v>
+        <v>571</v>
       </c>
       <c r="D75" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E75" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="F75" t="s">
-        <v>532</v>
+        <v>573</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>560</v>
+        <v>574</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="B76" t="s">
-        <v>238</v>
+        <v>381</v>
       </c>
       <c r="C76" t="s">
-        <v>239</v>
+        <v>189</v>
       </c>
       <c r="D76" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E76" t="s">
-        <v>562</v>
+        <v>576</v>
       </c>
       <c r="F76" t="s">
-        <v>241</v>
+        <v>382</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>563</v>
+        <v>577</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>578</v>
+      </c>
+      <c r="B77" t="s">
         <v>564</v>
       </c>
-      <c r="B77" t="s">
-        <v>565</v>
-      </c>
       <c r="C77" t="s">
-        <v>352</v>
+        <v>579</v>
       </c>
       <c r="D77" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E77" t="s">
-        <v>566</v>
+        <v>580</v>
       </c>
       <c r="F77" t="s">
         <v>567</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>568</v>
+        <v>581</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>569</v>
+        <v>582</v>
       </c>
       <c r="B78" t="s">
-        <v>570</v>
+        <v>583</v>
       </c>
       <c r="C78" t="s">
-        <v>571</v>
+        <v>189</v>
       </c>
       <c r="D78" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="E78" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="F78" t="s">
-        <v>573</v>
+        <v>213</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>575</v>
+        <v>586</v>
       </c>
       <c r="B79" t="s">
-        <v>576</v>
+        <v>587</v>
       </c>
       <c r="C79" t="s">
-        <v>577</v>
+        <v>588</v>
       </c>
       <c r="D79" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E79" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="F79" t="s">
-        <v>222</v>
+        <v>590</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="B80" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="C80" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="D80" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E80" t="s">
-        <v>583</v>
+        <v>237</v>
       </c>
       <c r="F80" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>585</v>
+        <v>596</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="B81" t="s">
-        <v>293</v>
+        <v>598</v>
       </c>
       <c r="C81" t="s">
-        <v>294</v>
+        <v>189</v>
       </c>
       <c r="D81" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E81" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="F81" t="s">
-        <v>296</v>
+        <v>329</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="B82" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="C82" t="s">
-        <v>400</v>
+        <v>603</v>
       </c>
       <c r="D82" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E82" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="F82" t="s">
-        <v>592</v>
+        <v>605</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>593</v>
+        <v>606</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>594</v>
+        <v>607</v>
       </c>
       <c r="B83" t="s">
-        <v>595</v>
+        <v>608</v>
       </c>
       <c r="C83" t="s">
-        <v>596</v>
+        <v>609</v>
       </c>
       <c r="D83" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E83" t="s">
-        <v>364</v>
+        <v>610</v>
       </c>
       <c r="F83" t="s">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>598</v>
+        <v>612</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>599</v>
+        <v>613</v>
       </c>
       <c r="B84" t="s">
-        <v>238</v>
+        <v>410</v>
       </c>
       <c r="C84" t="s">
-        <v>239</v>
+        <v>321</v>
       </c>
       <c r="D84" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E84" t="s">
-        <v>339</v>
+        <v>518</v>
       </c>
       <c r="F84" t="s">
-        <v>241</v>
+        <v>413</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>600</v>
+        <v>614</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="B85" t="s">
-        <v>602</v>
+        <v>616</v>
       </c>
       <c r="C85" t="s">
-        <v>239</v>
+        <v>189</v>
       </c>
       <c r="D85" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="E85" t="s">
-        <v>603</v>
+        <v>617</v>
       </c>
       <c r="F85" t="s">
-        <v>222</v>
+        <v>618</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>605</v>
+        <v>620</v>
       </c>
       <c r="B86" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
       <c r="C86" t="s">
-        <v>607</v>
+        <v>265</v>
       </c>
       <c r="D86" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E86" t="s">
-        <v>608</v>
+        <v>622</v>
       </c>
       <c r="F86" t="s">
-        <v>592</v>
+        <v>237</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>609</v>
+        <v>623</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>624</v>
+      </c>
+      <c r="B87" t="s">
+        <v>625</v>
+      </c>
+      <c r="C87" t="s">
+        <v>298</v>
+      </c>
+      <c r="D87" t="s">
+        <v>211</v>
+      </c>
+      <c r="E87" t="s">
+        <v>626</v>
+      </c>
+      <c r="F87" t="s">
+        <v>627</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>629</v>
+      </c>
+      <c r="B88" t="s">
+        <v>630</v>
+      </c>
+      <c r="C88" t="s">
+        <v>411</v>
+      </c>
+      <c r="D88" t="s">
+        <v>211</v>
+      </c>
+      <c r="E88" t="s">
+        <v>631</v>
+      </c>
+      <c r="F88" t="s">
+        <v>632</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>634</v>
+      </c>
+      <c r="B89" t="s">
+        <v>635</v>
+      </c>
+      <c r="C89" t="s">
+        <v>265</v>
+      </c>
+      <c r="D89" t="s">
+        <v>211</v>
+      </c>
+      <c r="E89" t="s">
+        <v>284</v>
+      </c>
+      <c r="F89" t="s">
+        <v>636</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>638</v>
+      </c>
+      <c r="B90" t="s">
+        <v>639</v>
+      </c>
+      <c r="C90" t="s">
+        <v>431</v>
+      </c>
+      <c r="D90" t="s">
+        <v>211</v>
+      </c>
+      <c r="E90" t="s">
+        <v>640</v>
+      </c>
+      <c r="F90" t="s">
+        <v>641</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>643</v>
+      </c>
+      <c r="B91" t="s">
+        <v>644</v>
+      </c>
+      <c r="C91" t="s">
+        <v>645</v>
+      </c>
+      <c r="D91" t="s">
+        <v>211</v>
+      </c>
+      <c r="E91" t="s">
+        <v>646</v>
+      </c>
+      <c r="F91" t="s">
+        <v>647</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>649</v>
+      </c>
+      <c r="B92" t="s">
+        <v>650</v>
+      </c>
+      <c r="C92" t="s">
+        <v>189</v>
+      </c>
+      <c r="D92" t="s">
+        <v>211</v>
+      </c>
+      <c r="E92" t="s">
+        <v>651</v>
+      </c>
+      <c r="F92" t="s">
+        <v>652</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>654</v>
+      </c>
+      <c r="B93" t="s">
+        <v>430</v>
+      </c>
+      <c r="C93" t="s">
+        <v>431</v>
+      </c>
+      <c r="D93" t="s">
+        <v>211</v>
+      </c>
+      <c r="E93" t="s">
+        <v>432</v>
+      </c>
+      <c r="F93" t="s">
+        <v>433</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>654</v>
+      </c>
+      <c r="B94" t="s">
+        <v>656</v>
+      </c>
+      <c r="C94" t="s">
+        <v>265</v>
+      </c>
+      <c r="D94" t="s">
+        <v>211</v>
+      </c>
+      <c r="E94" t="s">
+        <v>657</v>
+      </c>
+      <c r="F94" t="s">
+        <v>658</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>660</v>
+      </c>
+      <c r="B95" t="s">
+        <v>661</v>
+      </c>
+      <c r="C95" t="s">
+        <v>189</v>
+      </c>
+      <c r="D95" t="s">
+        <v>211</v>
+      </c>
+      <c r="E95" t="s">
+        <v>231</v>
+      </c>
+      <c r="F95" t="s">
+        <v>662</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>664</v>
+      </c>
+      <c r="B96" t="s">
+        <v>665</v>
+      </c>
+      <c r="C96" t="s">
+        <v>666</v>
+      </c>
+      <c r="D96" t="s">
+        <v>218</v>
+      </c>
+      <c r="E96" t="s">
+        <v>667</v>
+      </c>
+      <c r="F96" t="s">
+        <v>668</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>670</v>
+      </c>
+      <c r="B97" t="s">
+        <v>671</v>
+      </c>
+      <c r="C97" t="s">
+        <v>298</v>
+      </c>
+      <c r="D97" t="s">
+        <v>211</v>
+      </c>
+      <c r="E97" t="s">
+        <v>672</v>
+      </c>
+      <c r="F97" t="s">
+        <v>673</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>670</v>
+      </c>
+      <c r="B98" t="s">
+        <v>671</v>
+      </c>
+      <c r="C98" t="s">
+        <v>675</v>
+      </c>
+      <c r="D98" t="s">
+        <v>211</v>
+      </c>
+      <c r="E98" t="s">
+        <v>672</v>
+      </c>
+      <c r="F98" t="s">
+        <v>673</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>670</v>
+      </c>
+      <c r="B99" t="s">
+        <v>671</v>
+      </c>
+      <c r="C99" t="s">
+        <v>565</v>
+      </c>
+      <c r="D99" t="s">
+        <v>211</v>
+      </c>
+      <c r="E99" t="s">
+        <v>672</v>
+      </c>
+      <c r="F99" t="s">
+        <v>673</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>678</v>
+      </c>
+      <c r="B100" t="s">
+        <v>679</v>
+      </c>
+      <c r="C100" t="s">
+        <v>680</v>
+      </c>
+      <c r="D100" t="s">
+        <v>211</v>
+      </c>
+      <c r="E100" t="s">
+        <v>681</v>
+      </c>
+      <c r="F100" t="s">
+        <v>682</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>684</v>
+      </c>
+      <c r="B101" t="s">
+        <v>685</v>
+      </c>
+      <c r="C101" t="s">
+        <v>686</v>
+      </c>
+      <c r="D101" t="s">
+        <v>211</v>
+      </c>
+      <c r="E101" t="s">
+        <v>687</v>
+      </c>
+      <c r="F101" t="s">
+        <v>407</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>689</v>
+      </c>
+      <c r="B102" t="s">
+        <v>690</v>
+      </c>
+      <c r="C102" t="s">
+        <v>691</v>
+      </c>
+      <c r="D102" t="s">
+        <v>211</v>
+      </c>
+      <c r="E102" t="s">
+        <v>692</v>
+      </c>
+      <c r="F102" t="s">
+        <v>693</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>695</v>
+      </c>
+      <c r="B103" t="s">
+        <v>696</v>
+      </c>
+      <c r="C103" t="s">
+        <v>697</v>
+      </c>
+      <c r="D103" t="s">
+        <v>211</v>
+      </c>
+      <c r="E103" t="s">
+        <v>237</v>
+      </c>
+      <c r="F103" t="s">
+        <v>698</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>700</v>
+      </c>
+      <c r="B104" t="s">
+        <v>701</v>
+      </c>
+      <c r="C104" t="s">
+        <v>376</v>
+      </c>
+      <c r="D104" t="s">
+        <v>211</v>
+      </c>
+      <c r="E104" t="s">
+        <v>702</v>
+      </c>
+      <c r="F104" t="s">
+        <v>703</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>705</v>
+      </c>
+      <c r="B105" t="s">
+        <v>557</v>
+      </c>
+      <c r="C105" t="s">
+        <v>431</v>
+      </c>
+      <c r="D105" t="s">
+        <v>211</v>
+      </c>
+      <c r="E105" t="s">
+        <v>706</v>
+      </c>
+      <c r="F105" t="s">
+        <v>707</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>709</v>
+      </c>
+      <c r="B106" t="s">
+        <v>710</v>
+      </c>
+      <c r="C106" t="s">
+        <v>588</v>
+      </c>
+      <c r="D106" t="s">
+        <v>211</v>
+      </c>
+      <c r="E106" t="s">
+        <v>231</v>
+      </c>
+      <c r="F106" t="s">
+        <v>711</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>713</v>
+      </c>
+      <c r="B107" t="s">
+        <v>714</v>
+      </c>
+      <c r="C107" t="s">
+        <v>265</v>
+      </c>
+      <c r="D107" t="s">
+        <v>211</v>
+      </c>
+      <c r="E107" t="s">
+        <v>715</v>
+      </c>
+      <c r="F107" t="s">
+        <v>237</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>717</v>
+      </c>
+      <c r="B108" t="s">
+        <v>718</v>
+      </c>
+      <c r="C108" t="s">
+        <v>189</v>
+      </c>
+      <c r="D108" t="s">
+        <v>211</v>
+      </c>
+      <c r="E108" t="s">
+        <v>719</v>
+      </c>
+      <c r="F108" t="s">
+        <v>720</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>722</v>
+      </c>
+      <c r="B109" t="s">
+        <v>723</v>
+      </c>
+      <c r="C109" t="s">
+        <v>189</v>
+      </c>
+      <c r="D109" t="s">
+        <v>211</v>
+      </c>
+      <c r="E109" t="s">
+        <v>724</v>
+      </c>
+      <c r="F109" t="s">
+        <v>407</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>726</v>
+      </c>
+      <c r="B110" t="s">
+        <v>264</v>
+      </c>
+      <c r="C110" t="s">
+        <v>265</v>
+      </c>
+      <c r="D110" t="s">
+        <v>211</v>
+      </c>
+      <c r="E110" t="s">
+        <v>727</v>
+      </c>
+      <c r="F110" t="s">
+        <v>267</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>729</v>
+      </c>
+      <c r="B111" t="s">
+        <v>730</v>
+      </c>
+      <c r="C111" t="s">
+        <v>444</v>
+      </c>
+      <c r="D111" t="s">
+        <v>211</v>
+      </c>
+      <c r="E111" t="s">
+        <v>731</v>
+      </c>
+      <c r="F111" t="s">
+        <v>317</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>733</v>
+      </c>
+      <c r="B112" t="s">
+        <v>204</v>
+      </c>
+      <c r="C112" t="s">
+        <v>734</v>
+      </c>
+      <c r="D112" t="s">
+        <v>211</v>
+      </c>
+      <c r="E112" t="s">
+        <v>237</v>
+      </c>
+      <c r="F112" t="s">
+        <v>237</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>736</v>
+      </c>
+      <c r="B113" t="s">
+        <v>737</v>
+      </c>
+      <c r="C113" t="s">
+        <v>738</v>
+      </c>
+      <c r="D113" t="s">
+        <v>211</v>
+      </c>
+      <c r="E113" t="s">
+        <v>739</v>
+      </c>
+      <c r="F113" t="s">
+        <v>740</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>742</v>
+      </c>
+      <c r="B114" t="s">
+        <v>743</v>
+      </c>
+      <c r="C114" t="s">
+        <v>744</v>
+      </c>
+      <c r="D114" t="s">
+        <v>211</v>
+      </c>
+      <c r="E114" t="s">
+        <v>745</v>
+      </c>
+      <c r="F114" t="s">
+        <v>237</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>747</v>
+      </c>
+      <c r="B115" t="s">
+        <v>748</v>
+      </c>
+      <c r="C115" t="s">
+        <v>749</v>
+      </c>
+      <c r="D115" t="s">
+        <v>211</v>
+      </c>
+      <c r="E115" t="s">
+        <v>750</v>
+      </c>
+      <c r="F115" t="s">
+        <v>751</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>753</v>
+      </c>
+      <c r="B116" t="s">
+        <v>754</v>
+      </c>
+      <c r="C116" t="s">
+        <v>588</v>
+      </c>
+      <c r="D116" t="s">
+        <v>211</v>
+      </c>
+      <c r="E116" t="s">
+        <v>755</v>
+      </c>
+      <c r="F116" t="s">
+        <v>756</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>758</v>
+      </c>
+      <c r="B117" t="s">
+        <v>370</v>
+      </c>
+      <c r="C117" t="s">
+        <v>371</v>
+      </c>
+      <c r="D117" t="s">
+        <v>211</v>
+      </c>
+      <c r="E117" t="s">
+        <v>759</v>
+      </c>
+      <c r="F117" t="s">
+        <v>372</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>761</v>
+      </c>
+      <c r="B118" t="s">
+        <v>762</v>
+      </c>
+      <c r="C118" t="s">
+        <v>189</v>
+      </c>
+      <c r="D118" t="s">
+        <v>211</v>
+      </c>
+      <c r="E118" t="s">
+        <v>763</v>
+      </c>
+      <c r="F118" t="s">
+        <v>764</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>766</v>
+      </c>
+      <c r="B119" t="s">
+        <v>767</v>
+      </c>
+      <c r="C119" t="s">
+        <v>768</v>
+      </c>
+      <c r="D119" t="s">
+        <v>211</v>
+      </c>
+      <c r="E119" t="s">
+        <v>769</v>
+      </c>
+      <c r="F119" t="s">
+        <v>770</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>772</v>
+      </c>
+      <c r="B120" t="s">
+        <v>767</v>
+      </c>
+      <c r="C120" t="s">
+        <v>768</v>
+      </c>
+      <c r="D120" t="s">
+        <v>211</v>
+      </c>
+      <c r="E120" t="s">
+        <v>769</v>
+      </c>
+      <c r="F120" t="s">
+        <v>770</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>774</v>
+      </c>
+      <c r="B121" t="s">
+        <v>775</v>
+      </c>
+      <c r="C121" t="s">
+        <v>776</v>
+      </c>
+      <c r="D121" t="s">
+        <v>211</v>
+      </c>
+      <c r="E121" t="s">
+        <v>459</v>
+      </c>
+      <c r="F121" t="s">
+        <v>300</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>778</v>
+      </c>
+      <c r="B122" t="s">
+        <v>264</v>
+      </c>
+      <c r="C122" t="s">
+        <v>265</v>
+      </c>
+      <c r="D122" t="s">
+        <v>211</v>
+      </c>
+      <c r="E122" t="s">
+        <v>422</v>
+      </c>
+      <c r="F122" t="s">
+        <v>267</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>780</v>
+      </c>
+      <c r="B123" t="s">
+        <v>781</v>
+      </c>
+      <c r="C123" t="s">
+        <v>265</v>
+      </c>
+      <c r="D123" t="s">
+        <v>211</v>
+      </c>
+      <c r="E123" t="s">
+        <v>782</v>
+      </c>
+      <c r="F123" t="s">
+        <v>237</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>784</v>
+      </c>
+      <c r="B124" t="s">
+        <v>785</v>
+      </c>
+      <c r="C124" t="s">
+        <v>265</v>
+      </c>
+      <c r="D124" t="s">
+        <v>283</v>
+      </c>
+      <c r="E124" t="s">
+        <v>786</v>
+      </c>
+      <c r="F124" t="s">
+        <v>720</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>788</v>
+      </c>
+      <c r="B125" t="s">
+        <v>789</v>
+      </c>
+      <c r="C125" t="s">
+        <v>790</v>
+      </c>
+      <c r="D125" t="s">
+        <v>211</v>
+      </c>
+      <c r="E125" t="s">
+        <v>791</v>
+      </c>
+      <c r="F125" t="s">
+        <v>792</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>794</v>
+      </c>
+      <c r="B126" t="s">
+        <v>795</v>
+      </c>
+      <c r="C126" t="s">
+        <v>796</v>
+      </c>
+      <c r="D126" t="s">
+        <v>211</v>
+      </c>
+      <c r="E126" t="s">
+        <v>797</v>
+      </c>
+      <c r="F126" t="s">
+        <v>798</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>800</v>
+      </c>
+      <c r="B127" t="s">
+        <v>801</v>
+      </c>
+      <c r="C127" t="s">
+        <v>802</v>
+      </c>
+      <c r="D127" t="s">
+        <v>218</v>
+      </c>
+      <c r="E127" t="s">
+        <v>803</v>
+      </c>
+      <c r="F127" t="s">
+        <v>764</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>805</v>
+      </c>
+      <c r="B128" t="s">
+        <v>381</v>
+      </c>
+      <c r="C128" t="s">
+        <v>189</v>
+      </c>
+      <c r="D128" t="s">
+        <v>211</v>
+      </c>
+      <c r="E128" t="s">
+        <v>289</v>
+      </c>
+      <c r="F128" t="s">
+        <v>382</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>806</v>
       </c>
     </row>
   </sheetData>
@@ -5323,6 +6928,48 @@
     <hyperlink ref="H84" r:id="rId83"/>
     <hyperlink ref="H85" r:id="rId84"/>
     <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-10-26.xlsx
+++ b/docs/xlsx/jobs-2026-10-26.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="807">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="809">
   <si>
     <t>Title</t>
   </si>
@@ -2165,6 +2165,12 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/3dc2ef53fc554190b2ca0d6f9bc772f3-senior-hris-analyst-workday-research-foundation-of-cuny-new-york</t>
+  </si>
+  <si>
+    <t>Senior HRIS Analyst - Workday (Hybrid)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3dc2ef53fc554190b2ca0d6f9bc772f3-senior-hris-analyst-workday-hybrid-research-foundation-of-cuny-new-york</t>
   </si>
   <si>
     <t>Senior Software Development Engineer, Full Stack</t>
@@ -3880,7 +3886,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -6362,30 +6368,30 @@
         <v>717</v>
       </c>
       <c r="B108" t="s">
+        <v>714</v>
+      </c>
+      <c r="C108" t="s">
+        <v>265</v>
+      </c>
+      <c r="D108" t="s">
+        <v>211</v>
+      </c>
+      <c r="E108" t="s">
+        <v>715</v>
+      </c>
+      <c r="F108" t="s">
+        <v>237</v>
+      </c>
+      <c r="H108" s="2" t="s">
         <v>718</v>
-      </c>
-      <c r="C108" t="s">
-        <v>189</v>
-      </c>
-      <c r="D108" t="s">
-        <v>211</v>
-      </c>
-      <c r="E108" t="s">
-        <v>719</v>
-      </c>
-      <c r="F108" t="s">
-        <v>720</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B109" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="C109" t="s">
         <v>189</v>
@@ -6394,263 +6400,263 @@
         <v>211</v>
       </c>
       <c r="E109" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F109" t="s">
-        <v>407</v>
+        <v>722</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>724</v>
+      </c>
+      <c r="B110" t="s">
+        <v>725</v>
+      </c>
+      <c r="C110" t="s">
+        <v>189</v>
+      </c>
+      <c r="D110" t="s">
+        <v>211</v>
+      </c>
+      <c r="E110" t="s">
         <v>726</v>
       </c>
-      <c r="B110" t="s">
-        <v>264</v>
-      </c>
-      <c r="C110" t="s">
-        <v>265</v>
-      </c>
-      <c r="D110" t="s">
-        <v>211</v>
-      </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
+        <v>407</v>
+      </c>
+      <c r="H110" s="2" t="s">
         <v>727</v>
-      </c>
-      <c r="F110" t="s">
-        <v>267</v>
-      </c>
-      <c r="H110" s="2" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>728</v>
+      </c>
+      <c r="B111" t="s">
+        <v>264</v>
+      </c>
+      <c r="C111" t="s">
+        <v>265</v>
+      </c>
+      <c r="D111" t="s">
+        <v>211</v>
+      </c>
+      <c r="E111" t="s">
         <v>729</v>
       </c>
-      <c r="B111" t="s">
+      <c r="F111" t="s">
+        <v>267</v>
+      </c>
+      <c r="H111" s="2" t="s">
         <v>730</v>
-      </c>
-      <c r="C111" t="s">
-        <v>444</v>
-      </c>
-      <c r="D111" t="s">
-        <v>211</v>
-      </c>
-      <c r="E111" t="s">
-        <v>731</v>
-      </c>
-      <c r="F111" t="s">
-        <v>317</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>731</v>
+      </c>
+      <c r="B112" t="s">
+        <v>732</v>
+      </c>
+      <c r="C112" t="s">
+        <v>444</v>
+      </c>
+      <c r="D112" t="s">
+        <v>211</v>
+      </c>
+      <c r="E112" t="s">
         <v>733</v>
       </c>
-      <c r="B112" t="s">
-        <v>204</v>
-      </c>
-      <c r="C112" t="s">
+      <c r="F112" t="s">
+        <v>317</v>
+      </c>
+      <c r="H112" s="2" t="s">
         <v>734</v>
-      </c>
-      <c r="D112" t="s">
-        <v>211</v>
-      </c>
-      <c r="E112" t="s">
-        <v>237</v>
-      </c>
-      <c r="F112" t="s">
-        <v>237</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>735</v>
+      </c>
+      <c r="B113" t="s">
+        <v>204</v>
+      </c>
+      <c r="C113" t="s">
         <v>736</v>
       </c>
-      <c r="B113" t="s">
+      <c r="D113" t="s">
+        <v>211</v>
+      </c>
+      <c r="E113" t="s">
+        <v>237</v>
+      </c>
+      <c r="F113" t="s">
+        <v>237</v>
+      </c>
+      <c r="H113" s="2" t="s">
         <v>737</v>
-      </c>
-      <c r="C113" t="s">
-        <v>738</v>
-      </c>
-      <c r="D113" t="s">
-        <v>211</v>
-      </c>
-      <c r="E113" t="s">
-        <v>739</v>
-      </c>
-      <c r="F113" t="s">
-        <v>740</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>738</v>
+      </c>
+      <c r="B114" t="s">
+        <v>739</v>
+      </c>
+      <c r="C114" t="s">
+        <v>740</v>
+      </c>
+      <c r="D114" t="s">
+        <v>211</v>
+      </c>
+      <c r="E114" t="s">
+        <v>741</v>
+      </c>
+      <c r="F114" t="s">
         <v>742</v>
       </c>
-      <c r="B114" t="s">
+      <c r="H114" s="2" t="s">
         <v>743</v>
-      </c>
-      <c r="C114" t="s">
-        <v>744</v>
-      </c>
-      <c r="D114" t="s">
-        <v>211</v>
-      </c>
-      <c r="E114" t="s">
-        <v>745</v>
-      </c>
-      <c r="F114" t="s">
-        <v>237</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>744</v>
+      </c>
+      <c r="B115" t="s">
+        <v>745</v>
+      </c>
+      <c r="C115" t="s">
+        <v>746</v>
+      </c>
+      <c r="D115" t="s">
+        <v>211</v>
+      </c>
+      <c r="E115" t="s">
         <v>747</v>
       </c>
-      <c r="B115" t="s">
+      <c r="F115" t="s">
+        <v>237</v>
+      </c>
+      <c r="H115" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="C115" t="s">
-        <v>749</v>
-      </c>
-      <c r="D115" t="s">
-        <v>211</v>
-      </c>
-      <c r="E115" t="s">
-        <v>750</v>
-      </c>
-      <c r="F115" t="s">
-        <v>751</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>749</v>
+      </c>
+      <c r="B116" t="s">
+        <v>750</v>
+      </c>
+      <c r="C116" t="s">
+        <v>751</v>
+      </c>
+      <c r="D116" t="s">
+        <v>211</v>
+      </c>
+      <c r="E116" t="s">
+        <v>752</v>
+      </c>
+      <c r="F116" t="s">
         <v>753</v>
       </c>
-      <c r="B116" t="s">
+      <c r="H116" s="2" t="s">
         <v>754</v>
-      </c>
-      <c r="C116" t="s">
-        <v>588</v>
-      </c>
-      <c r="D116" t="s">
-        <v>211</v>
-      </c>
-      <c r="E116" t="s">
-        <v>755</v>
-      </c>
-      <c r="F116" t="s">
-        <v>756</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>755</v>
+      </c>
+      <c r="B117" t="s">
+        <v>756</v>
+      </c>
+      <c r="C117" t="s">
+        <v>588</v>
+      </c>
+      <c r="D117" t="s">
+        <v>211</v>
+      </c>
+      <c r="E117" t="s">
+        <v>757</v>
+      </c>
+      <c r="F117" t="s">
         <v>758</v>
       </c>
-      <c r="B117" t="s">
-        <v>370</v>
-      </c>
-      <c r="C117" t="s">
-        <v>371</v>
-      </c>
-      <c r="D117" t="s">
-        <v>211</v>
-      </c>
-      <c r="E117" t="s">
+      <c r="H117" s="2" t="s">
         <v>759</v>
-      </c>
-      <c r="F117" t="s">
-        <v>372</v>
-      </c>
-      <c r="H117" s="2" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>760</v>
+      </c>
+      <c r="B118" t="s">
+        <v>370</v>
+      </c>
+      <c r="C118" t="s">
+        <v>371</v>
+      </c>
+      <c r="D118" t="s">
+        <v>211</v>
+      </c>
+      <c r="E118" t="s">
         <v>761</v>
       </c>
-      <c r="B118" t="s">
+      <c r="F118" t="s">
+        <v>372</v>
+      </c>
+      <c r="H118" s="2" t="s">
         <v>762</v>
-      </c>
-      <c r="C118" t="s">
-        <v>189</v>
-      </c>
-      <c r="D118" t="s">
-        <v>211</v>
-      </c>
-      <c r="E118" t="s">
-        <v>763</v>
-      </c>
-      <c r="F118" t="s">
-        <v>764</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>763</v>
+      </c>
+      <c r="B119" t="s">
+        <v>764</v>
+      </c>
+      <c r="C119" t="s">
+        <v>189</v>
+      </c>
+      <c r="D119" t="s">
+        <v>211</v>
+      </c>
+      <c r="E119" t="s">
+        <v>765</v>
+      </c>
+      <c r="F119" t="s">
         <v>766</v>
       </c>
-      <c r="B119" t="s">
+      <c r="H119" s="2" t="s">
         <v>767</v>
-      </c>
-      <c r="C119" t="s">
-        <v>768</v>
-      </c>
-      <c r="D119" t="s">
-        <v>211</v>
-      </c>
-      <c r="E119" t="s">
-        <v>769</v>
-      </c>
-      <c r="F119" t="s">
-        <v>770</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>768</v>
+      </c>
+      <c r="B120" t="s">
+        <v>769</v>
+      </c>
+      <c r="C120" t="s">
+        <v>770</v>
+      </c>
+      <c r="D120" t="s">
+        <v>211</v>
+      </c>
+      <c r="E120" t="s">
+        <v>771</v>
+      </c>
+      <c r="F120" t="s">
         <v>772</v>
-      </c>
-      <c r="B120" t="s">
-        <v>767</v>
-      </c>
-      <c r="C120" t="s">
-        <v>768</v>
-      </c>
-      <c r="D120" t="s">
-        <v>211</v>
-      </c>
-      <c r="E120" t="s">
-        <v>769</v>
-      </c>
-      <c r="F120" t="s">
-        <v>770</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>773</v>
@@ -6661,42 +6667,42 @@
         <v>774</v>
       </c>
       <c r="B121" t="s">
+        <v>769</v>
+      </c>
+      <c r="C121" t="s">
+        <v>770</v>
+      </c>
+      <c r="D121" t="s">
+        <v>211</v>
+      </c>
+      <c r="E121" t="s">
+        <v>771</v>
+      </c>
+      <c r="F121" t="s">
+        <v>772</v>
+      </c>
+      <c r="H121" s="2" t="s">
         <v>775</v>
-      </c>
-      <c r="C121" t="s">
-        <v>776</v>
-      </c>
-      <c r="D121" t="s">
-        <v>211</v>
-      </c>
-      <c r="E121" t="s">
-        <v>459</v>
-      </c>
-      <c r="F121" t="s">
-        <v>300</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>776</v>
+      </c>
+      <c r="B122" t="s">
+        <v>777</v>
+      </c>
+      <c r="C122" t="s">
         <v>778</v>
       </c>
-      <c r="B122" t="s">
-        <v>264</v>
-      </c>
-      <c r="C122" t="s">
-        <v>265</v>
-      </c>
       <c r="D122" t="s">
         <v>211</v>
       </c>
       <c r="E122" t="s">
-        <v>422</v>
+        <v>459</v>
       </c>
       <c r="F122" t="s">
-        <v>267</v>
+        <v>300</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>779</v>
@@ -6707,7 +6713,7 @@
         <v>780</v>
       </c>
       <c r="B123" t="s">
-        <v>781</v>
+        <v>264</v>
       </c>
       <c r="C123" t="s">
         <v>265</v>
@@ -6716,128 +6722,151 @@
         <v>211</v>
       </c>
       <c r="E123" t="s">
-        <v>782</v>
+        <v>422</v>
       </c>
       <c r="F123" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B124" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C124" t="s">
         <v>265</v>
       </c>
       <c r="D124" t="s">
-        <v>283</v>
+        <v>211</v>
       </c>
       <c r="E124" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="F124" t="s">
-        <v>720</v>
+        <v>237</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>786</v>
+      </c>
+      <c r="B125" t="s">
+        <v>787</v>
+      </c>
+      <c r="C125" t="s">
+        <v>265</v>
+      </c>
+      <c r="D125" t="s">
+        <v>283</v>
+      </c>
+      <c r="E125" t="s">
         <v>788</v>
       </c>
-      <c r="B125" t="s">
+      <c r="F125" t="s">
+        <v>722</v>
+      </c>
+      <c r="H125" s="2" t="s">
         <v>789</v>
-      </c>
-      <c r="C125" t="s">
-        <v>790</v>
-      </c>
-      <c r="D125" t="s">
-        <v>211</v>
-      </c>
-      <c r="E125" t="s">
-        <v>791</v>
-      </c>
-      <c r="F125" t="s">
-        <v>792</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>790</v>
+      </c>
+      <c r="B126" t="s">
+        <v>791</v>
+      </c>
+      <c r="C126" t="s">
+        <v>792</v>
+      </c>
+      <c r="D126" t="s">
+        <v>211</v>
+      </c>
+      <c r="E126" t="s">
+        <v>793</v>
+      </c>
+      <c r="F126" t="s">
         <v>794</v>
       </c>
-      <c r="B126" t="s">
+      <c r="H126" s="2" t="s">
         <v>795</v>
-      </c>
-      <c r="C126" t="s">
-        <v>796</v>
-      </c>
-      <c r="D126" t="s">
-        <v>211</v>
-      </c>
-      <c r="E126" t="s">
-        <v>797</v>
-      </c>
-      <c r="F126" t="s">
-        <v>798</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>796</v>
+      </c>
+      <c r="B127" t="s">
+        <v>797</v>
+      </c>
+      <c r="C127" t="s">
+        <v>798</v>
+      </c>
+      <c r="D127" t="s">
+        <v>211</v>
+      </c>
+      <c r="E127" t="s">
+        <v>799</v>
+      </c>
+      <c r="F127" t="s">
         <v>800</v>
       </c>
-      <c r="B127" t="s">
+      <c r="H127" s="2" t="s">
         <v>801</v>
-      </c>
-      <c r="C127" t="s">
-        <v>802</v>
-      </c>
-      <c r="D127" t="s">
-        <v>218</v>
-      </c>
-      <c r="E127" t="s">
-        <v>803</v>
-      </c>
-      <c r="F127" t="s">
-        <v>764</v>
-      </c>
-      <c r="H127" s="2" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>802</v>
+      </c>
+      <c r="B128" t="s">
+        <v>803</v>
+      </c>
+      <c r="C128" t="s">
+        <v>804</v>
+      </c>
+      <c r="D128" t="s">
+        <v>218</v>
+      </c>
+      <c r="E128" t="s">
         <v>805</v>
       </c>
-      <c r="B128" t="s">
-        <v>381</v>
-      </c>
-      <c r="C128" t="s">
-        <v>189</v>
-      </c>
-      <c r="D128" t="s">
-        <v>211</v>
-      </c>
-      <c r="E128" t="s">
-        <v>289</v>
-      </c>
       <c r="F128" t="s">
-        <v>382</v>
+        <v>766</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>806</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>807</v>
+      </c>
+      <c r="B129" t="s">
+        <v>381</v>
+      </c>
+      <c r="C129" t="s">
+        <v>189</v>
+      </c>
+      <c r="D129" t="s">
+        <v>211</v>
+      </c>
+      <c r="E129" t="s">
+        <v>289</v>
+      </c>
+      <c r="F129" t="s">
+        <v>382</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>808</v>
       </c>
     </row>
   </sheetData>
@@ -6970,6 +6999,7 @@
     <hyperlink ref="H126" r:id="rId125"/>
     <hyperlink ref="H127" r:id="rId126"/>
     <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
